--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E862211-58BB-4324-B5BC-88EEB06224C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A754C2-D0C0-4EB0-8F0D-99705D4332A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1950" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -3249,7 +3249,7 @@
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2">
         <v>46061</v>
@@ -3266,7 +3266,7 @@
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F49" s="2">
         <v>46061</v>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F50" s="2">
         <v>46061</v>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F51" s="2">
         <v>46061</v>
@@ -3317,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F52" s="2">
         <v>46061</v>
@@ -3334,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F53" s="2">
         <v>46061</v>
@@ -3368,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2">
         <v>46061</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E862211-58BB-4324-B5BC-88EEB06224C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372745F4-4B41-4675-93F7-C2E50D3456B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F51" s="2">
         <v>46061</v>
@@ -3317,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F52" s="2">
         <v>46061</v>
@@ -3334,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F53" s="2">
         <v>46061</v>
@@ -3368,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2">
         <v>46061</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A754C2-D0C0-4EB0-8F0D-99705D4332A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372745F4-4B41-4675-93F7-C2E50D3456B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -3249,7 +3249,7 @@
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F48" s="2">
         <v>46061</v>
@@ -3266,7 +3266,7 @@
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F49" s="2">
         <v>46061</v>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F50" s="2">
         <v>46061</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372745F4-4B41-4675-93F7-C2E50D3456B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E862211-58BB-4324-B5BC-88EEB06224C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F51" s="2">
         <v>46061</v>
@@ -3317,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F52" s="2">
         <v>46061</v>
@@ -3334,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F53" s="2">
         <v>46061</v>
@@ -3368,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>675</v>
       </c>
       <c r="F55" s="2">
         <v>46061</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E862211-58BB-4324-B5BC-88EEB06224C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C771EC6-F31F-46AF-AE24-908C8CDCA34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -565,9 +565,6 @@
     <t>057-python-lab-implement-focal-loss.md</t>
   </si>
   <si>
-    <t xml:space="preserve">Добавить Focal Loss как альтернативу CrossEntropy. Она фокусирует обучение на "сложных" примерах, где модель чаще ошибается. </t>
-  </si>
-  <si>
     <t>058-python-lab-backtest-slippage-model.md</t>
   </si>
   <si>
@@ -2066,6 +2063,9 @@
   </si>
   <si>
     <t>ПРОВЕРЕНО</t>
+  </si>
+  <si>
+    <t>Добавить Focal Loss как альтернативу CrossEntropy. Она фокусирует обучение на "сложных" примерах, где модель чаще ошибается. Focal Loss и Label Smoothing — альтернативные методы. Рекомендуется проводить ablation studies перед их одновременным использованием</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F5" s="2">
         <v>46060</v>
@@ -2559,7 +2559,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F6" s="2">
         <v>46060</v>
@@ -2579,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F7" s="2">
         <v>46060</v>
@@ -2599,7 +2599,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F8" s="2">
         <v>46060</v>
@@ -2619,7 +2619,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F9" s="2">
         <v>46060</v>
@@ -2639,7 +2639,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F10" s="2">
         <v>46060</v>
@@ -2659,7 +2659,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F11" s="2">
         <v>46060</v>
@@ -2679,7 +2679,7 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F12" s="2">
         <v>46060</v>
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F14" s="2">
         <v>46060</v>
@@ -2724,7 +2724,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F15" s="2">
         <v>46060</v>
@@ -2741,7 +2741,7 @@
         <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F16" s="2">
         <v>46060</v>
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F17" s="2">
         <v>46060</v>
@@ -2775,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F18" s="2">
         <v>46060</v>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F19" s="2">
         <v>46060</v>
@@ -2809,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F20" s="2">
         <v>46060</v>
@@ -2826,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F21" s="2">
         <v>46060</v>
@@ -2843,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F22" s="2">
         <v>46060</v>
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F23" s="2">
         <v>46060</v>
@@ -2877,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F24" s="2">
         <v>46060</v>
@@ -2899,7 +2899,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F26" s="2">
         <v>46060</v>
@@ -2916,7 +2916,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F27" s="2">
         <v>46060</v>
@@ -2933,7 +2933,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F28" s="2">
         <v>46060</v>
@@ -2950,7 +2950,7 @@
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F29" s="2">
         <v>46060</v>
@@ -2967,7 +2967,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F30" s="2">
         <v>46060</v>
@@ -2984,7 +2984,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F31" s="2">
         <v>46060</v>
@@ -3001,7 +3001,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F32" s="2">
         <v>46060</v>
@@ -3018,7 +3018,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F33" s="2">
         <v>46060</v>
@@ -3035,7 +3035,7 @@
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F34" s="2">
         <v>46060</v>
@@ -3052,7 +3052,7 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F35" s="2">
         <v>46060</v>
@@ -3063,13 +3063,13 @@
         <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F36" s="2">
         <v>46060</v>
@@ -3086,7 +3086,7 @@
         <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F37" s="2">
         <v>46060</v>
@@ -3108,7 +3108,7 @@
         <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F39" s="2">
         <v>46060</v>
@@ -3125,7 +3125,7 @@
         <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F40" s="2">
         <v>46060</v>
@@ -3142,7 +3142,7 @@
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F41" s="2">
         <v>46060</v>
@@ -3159,7 +3159,7 @@
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F42" s="2">
         <v>46060</v>
@@ -3176,7 +3176,7 @@
         <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F43" s="2">
         <v>46060</v>
@@ -3193,7 +3193,7 @@
         <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F44" s="2">
         <v>46061</v>
@@ -3215,7 +3215,7 @@
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F46" s="2">
         <v>46061</v>
@@ -3232,7 +3232,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F47" s="2">
         <v>46061</v>
@@ -3249,7 +3249,7 @@
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F48" s="2">
         <v>46061</v>
@@ -3266,7 +3266,7 @@
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F49" s="2">
         <v>46061</v>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F50" s="2">
         <v>46061</v>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F51" s="2">
         <v>46061</v>
@@ -3317,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F52" s="2">
         <v>46061</v>
@@ -3334,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F53" s="2">
         <v>46061</v>
@@ -3351,7 +3351,7 @@
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F54" s="2">
         <v>46061</v>
@@ -3368,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F55" s="2">
         <v>46061</v>
@@ -3385,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F56" s="2">
         <v>46061</v>
@@ -3402,7 +3402,7 @@
         <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F57" s="2">
         <v>46061</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
@@ -3424,7 +3424,7 @@
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F59" s="2">
         <v>46061</v>
@@ -3441,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F60" s="2">
         <v>46061</v>
@@ -3458,7 +3458,7 @@
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F61" s="2">
         <v>46061</v>
@@ -3475,7 +3475,7 @@
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F62" s="2">
         <v>46061</v>
@@ -3492,7 +3492,7 @@
         <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F63" s="2">
         <v>46061</v>
@@ -3509,7 +3509,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F64" s="2">
         <v>46061</v>
@@ -3520,7 +3520,7 @@
         <v>174</v>
       </c>
       <c r="C65" t="s">
-        <v>175</v>
+        <v>675</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" t="s">
         <v>176</v>
-      </c>
-      <c r="C66" t="s">
-        <v>177</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
+        <v>177</v>
+      </c>
+      <c r="C67" t="s">
         <v>178</v>
-      </c>
-      <c r="C67" t="s">
-        <v>179</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
+        <v>179</v>
+      </c>
+      <c r="C68" t="s">
         <v>180</v>
-      </c>
-      <c r="C68" t="s">
-        <v>181</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" t="s">
         <v>182</v>
-      </c>
-      <c r="C70" t="s">
-        <v>183</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" t="s">
         <v>184</v>
-      </c>
-      <c r="C71" t="s">
-        <v>185</v>
       </c>
       <c r="D71" t="s">
         <v>4</v>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" t="s">
         <v>186</v>
-      </c>
-      <c r="C72" t="s">
-        <v>187</v>
       </c>
       <c r="D72" t="s">
         <v>4</v>
@@ -3641,10 +3641,10 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73" t="s">
         <v>188</v>
-      </c>
-      <c r="C73" t="s">
-        <v>189</v>
       </c>
       <c r="D73" t="s">
         <v>4</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" t="s">
         <v>190</v>
-      </c>
-      <c r="C74" t="s">
-        <v>191</v>
       </c>
       <c r="D74" t="s">
         <v>4</v>
@@ -3675,13 +3675,13 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" t="s">
         <v>192</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>193</v>
-      </c>
-      <c r="D75" t="s">
-        <v>194</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" t="s">
         <v>195</v>
-      </c>
-      <c r="C76" t="s">
-        <v>196</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" t="s">
         <v>197</v>
-      </c>
-      <c r="C77" t="s">
-        <v>198</v>
       </c>
       <c r="D77" t="s">
         <v>4</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78" t="s">
         <v>199</v>
-      </c>
-      <c r="C78" t="s">
-        <v>200</v>
       </c>
       <c r="D78" t="s">
         <v>4</v>
@@ -3743,13 +3743,13 @@
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
+        <v>200</v>
+      </c>
+      <c r="C79" t="s">
         <v>201</v>
       </c>
-      <c r="C79" t="s">
-        <v>202</v>
-      </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" t="s">
         <v>203</v>
-      </c>
-      <c r="C81" t="s">
-        <v>204</v>
       </c>
       <c r="D81" t="s">
         <v>4</v>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" t="s">
         <v>205</v>
-      </c>
-      <c r="C82" t="s">
-        <v>206</v>
       </c>
       <c r="D82" t="s">
         <v>4</v>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
+        <v>206</v>
+      </c>
+      <c r="C83" t="s">
         <v>207</v>
-      </c>
-      <c r="C83" t="s">
-        <v>208</v>
       </c>
       <c r="D83" t="s">
         <v>4</v>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" t="s">
         <v>209</v>
-      </c>
-      <c r="C84" t="s">
-        <v>210</v>
       </c>
       <c r="D84" t="s">
         <v>4</v>
@@ -3833,10 +3833,10 @@
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
+        <v>210</v>
+      </c>
+      <c r="C85" t="s">
         <v>211</v>
-      </c>
-      <c r="C85" t="s">
-        <v>212</v>
       </c>
       <c r="D85" t="s">
         <v>4</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" t="s">
         <v>213</v>
-      </c>
-      <c r="C87" t="s">
-        <v>214</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C89" t="s">
         <v>217</v>
-      </c>
-      <c r="C89" t="s">
-        <v>218</v>
       </c>
       <c r="D89" t="s">
         <v>1</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" t="s">
         <v>219</v>
-      </c>
-      <c r="C90" t="s">
-        <v>220</v>
       </c>
       <c r="D90" t="s">
         <v>1</v>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
+        <v>220</v>
+      </c>
+      <c r="C91" t="s">
         <v>221</v>
-      </c>
-      <c r="C91" t="s">
-        <v>222</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
@@ -3945,13 +3945,13 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" t="s">
         <v>223</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>224</v>
-      </c>
-      <c r="D93" t="s">
-        <v>225</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -3962,13 +3962,13 @@
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" t="s">
         <v>226</v>
       </c>
-      <c r="C94" t="s">
-        <v>227</v>
-      </c>
       <c r="D94" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" t="s">
         <v>228</v>
-      </c>
-      <c r="C95" t="s">
-        <v>229</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C96" t="s">
         <v>230</v>
-      </c>
-      <c r="C96" t="s">
-        <v>231</v>
       </c>
       <c r="D96" t="s">
         <v>4</v>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
+        <v>231</v>
+      </c>
+      <c r="C97" t="s">
         <v>232</v>
-      </c>
-      <c r="C97" t="s">
-        <v>233</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -4028,7 +4028,7 @@
         <v>46063</v>
       </c>
       <c r="G97" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.25">
@@ -4038,10 +4038,10 @@
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
+        <v>233</v>
+      </c>
+      <c r="C99" t="s">
         <v>234</v>
-      </c>
-      <c r="C99" t="s">
-        <v>235</v>
       </c>
       <c r="D99" t="s">
         <v>19</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
+        <v>235</v>
+      </c>
+      <c r="C100" t="s">
         <v>236</v>
-      </c>
-      <c r="C100" t="s">
-        <v>237</v>
       </c>
       <c r="D100" t="s">
         <v>19</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
+        <v>237</v>
+      </c>
+      <c r="C101" t="s">
         <v>238</v>
-      </c>
-      <c r="C101" t="s">
-        <v>239</v>
       </c>
       <c r="D101" t="s">
         <v>19</v>
@@ -4089,10 +4089,10 @@
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
+        <v>239</v>
+      </c>
+      <c r="C102" t="s">
         <v>240</v>
-      </c>
-      <c r="C102" t="s">
-        <v>241</v>
       </c>
       <c r="D102" t="s">
         <v>19</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
+        <v>241</v>
+      </c>
+      <c r="C103" t="s">
         <v>242</v>
-      </c>
-      <c r="C103" t="s">
-        <v>243</v>
       </c>
       <c r="D103" t="s">
         <v>19</v>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
+        <v>243</v>
+      </c>
+      <c r="C105" t="s">
         <v>244</v>
-      </c>
-      <c r="C105" t="s">
-        <v>245</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
+        <v>245</v>
+      </c>
+      <c r="C106" t="s">
         <v>246</v>
-      </c>
-      <c r="C106" t="s">
-        <v>247</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
+        <v>247</v>
+      </c>
+      <c r="C107" t="s">
         <v>248</v>
-      </c>
-      <c r="C107" t="s">
-        <v>249</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" t="s">
         <v>250</v>
-      </c>
-      <c r="C108" t="s">
-        <v>251</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
+        <v>251</v>
+      </c>
+      <c r="C109" t="s">
         <v>252</v>
-      </c>
-      <c r="C109" t="s">
-        <v>253</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
+        <v>253</v>
+      </c>
+      <c r="C111" t="s">
         <v>254</v>
-      </c>
-      <c r="C111" t="s">
-        <v>255</v>
       </c>
       <c r="D111" t="s">
         <v>17</v>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
+        <v>255</v>
+      </c>
+      <c r="C112" t="s">
         <v>256</v>
-      </c>
-      <c r="C112" t="s">
-        <v>257</v>
       </c>
       <c r="D112" t="s">
         <v>17</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
+        <v>257</v>
+      </c>
+      <c r="C113" t="s">
         <v>258</v>
-      </c>
-      <c r="C113" t="s">
-        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>17</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
+        <v>259</v>
+      </c>
+      <c r="C114" t="s">
         <v>260</v>
-      </c>
-      <c r="C114" t="s">
-        <v>261</v>
       </c>
       <c r="D114" t="s">
         <v>17</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
+        <v>261</v>
+      </c>
+      <c r="C115" t="s">
         <v>262</v>
-      </c>
-      <c r="C115" t="s">
-        <v>263</v>
       </c>
       <c r="D115" t="s">
         <v>17</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" t="s">
         <v>264</v>
-      </c>
-      <c r="C117" t="s">
-        <v>265</v>
       </c>
       <c r="D117" t="s">
         <v>4</v>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" t="s">
         <v>266</v>
-      </c>
-      <c r="C118" t="s">
-        <v>267</v>
       </c>
       <c r="D118" t="s">
         <v>4</v>
@@ -4342,10 +4342,10 @@
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" t="s">
         <v>268</v>
-      </c>
-      <c r="C119" t="s">
-        <v>269</v>
       </c>
       <c r="D119" t="s">
         <v>4</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
+        <v>269</v>
+      </c>
+      <c r="C120" t="s">
         <v>270</v>
-      </c>
-      <c r="C120" t="s">
-        <v>271</v>
       </c>
       <c r="D120" t="s">
         <v>4</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
+        <v>271</v>
+      </c>
+      <c r="C121" t="s">
         <v>272</v>
-      </c>
-      <c r="C121" t="s">
-        <v>273</v>
       </c>
       <c r="D121" t="s">
         <v>4</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" t="s">
         <v>274</v>
-      </c>
-      <c r="C122" t="s">
-        <v>275</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
@@ -4410,10 +4410,10 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" t="s">
         <v>276</v>
-      </c>
-      <c r="C123" t="s">
-        <v>277</v>
       </c>
       <c r="D123" t="s">
         <v>4</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
+        <v>277</v>
+      </c>
+      <c r="C124" t="s">
         <v>278</v>
-      </c>
-      <c r="C124" t="s">
-        <v>279</v>
       </c>
       <c r="D124" t="s">
         <v>4</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
+        <v>279</v>
+      </c>
+      <c r="C125" t="s">
         <v>280</v>
-      </c>
-      <c r="C125" t="s">
-        <v>281</v>
       </c>
       <c r="D125" t="s">
         <v>4</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
+        <v>281</v>
+      </c>
+      <c r="C126" t="s">
         <v>282</v>
-      </c>
-      <c r="C126" t="s">
-        <v>283</v>
       </c>
       <c r="D126" t="s">
         <v>4</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
+        <v>283</v>
+      </c>
+      <c r="C128" t="s">
         <v>284</v>
-      </c>
-      <c r="C128" t="s">
-        <v>285</v>
       </c>
       <c r="D128" t="s">
         <v>4</v>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
+        <v>285</v>
+      </c>
+      <c r="C129" t="s">
         <v>286</v>
-      </c>
-      <c r="C129" t="s">
-        <v>287</v>
       </c>
       <c r="D129" t="s">
         <v>4</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
+        <v>287</v>
+      </c>
+      <c r="C130" t="s">
         <v>288</v>
-      </c>
-      <c r="C130" t="s">
-        <v>289</v>
       </c>
       <c r="D130" t="s">
         <v>4</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
+        <v>289</v>
+      </c>
+      <c r="C131" t="s">
         <v>290</v>
-      </c>
-      <c r="C131" t="s">
-        <v>291</v>
       </c>
       <c r="D131" t="s">
         <v>4</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
+        <v>291</v>
+      </c>
+      <c r="C132" t="s">
         <v>292</v>
-      </c>
-      <c r="C132" t="s">
-        <v>293</v>
       </c>
       <c r="D132" t="s">
         <v>4</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
+        <v>293</v>
+      </c>
+      <c r="C133" t="s">
         <v>294</v>
-      </c>
-      <c r="C133" t="s">
-        <v>295</v>
       </c>
       <c r="D133" t="s">
         <v>4</v>
@@ -4585,10 +4585,10 @@
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C134" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D134" t="s">
         <v>4</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
+        <v>296</v>
+      </c>
+      <c r="C135" t="s">
         <v>297</v>
-      </c>
-      <c r="C135" t="s">
-        <v>298</v>
       </c>
       <c r="D135" t="s">
         <v>4</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
+        <v>298</v>
+      </c>
+      <c r="C136" t="s">
         <v>299</v>
-      </c>
-      <c r="C136" t="s">
-        <v>300</v>
       </c>
       <c r="D136" t="s">
         <v>4</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
+        <v>300</v>
+      </c>
+      <c r="C137" t="s">
         <v>301</v>
-      </c>
-      <c r="C137" t="s">
-        <v>302</v>
       </c>
       <c r="D137" t="s">
         <v>4</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
+        <v>302</v>
+      </c>
+      <c r="C139" t="s">
         <v>303</v>
-      </c>
-      <c r="C139" t="s">
-        <v>304</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -4675,10 +4675,10 @@
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
+        <v>304</v>
+      </c>
+      <c r="C140" t="s">
         <v>305</v>
-      </c>
-      <c r="C140" t="s">
-        <v>306</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
+        <v>306</v>
+      </c>
+      <c r="C141" t="s">
         <v>307</v>
-      </c>
-      <c r="C141" t="s">
-        <v>308</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -4709,10 +4709,10 @@
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
+        <v>308</v>
+      </c>
+      <c r="C142" t="s">
         <v>309</v>
-      </c>
-      <c r="C142" t="s">
-        <v>310</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -4726,10 +4726,10 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
+        <v>310</v>
+      </c>
+      <c r="C143" t="s">
         <v>311</v>
-      </c>
-      <c r="C143" t="s">
-        <v>312</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" t="s">
         <v>313</v>
-      </c>
-      <c r="C144" t="s">
-        <v>314</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" t="s">
         <v>315</v>
-      </c>
-      <c r="C145" t="s">
-        <v>316</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
+        <v>316</v>
+      </c>
+      <c r="C146" t="s">
         <v>317</v>
-      </c>
-      <c r="C146" t="s">
-        <v>318</v>
       </c>
       <c r="D146" t="s">
         <v>17</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
+        <v>318</v>
+      </c>
+      <c r="C147" t="s">
         <v>319</v>
-      </c>
-      <c r="C147" t="s">
-        <v>320</v>
       </c>
       <c r="D147" t="s">
         <v>17</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
+        <v>320</v>
+      </c>
+      <c r="C148" t="s">
         <v>321</v>
-      </c>
-      <c r="C148" t="s">
-        <v>322</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -4833,10 +4833,10 @@
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
+        <v>322</v>
+      </c>
+      <c r="C150" t="s">
         <v>323</v>
-      </c>
-      <c r="C150" t="s">
-        <v>324</v>
       </c>
       <c r="D150" t="s">
         <v>1</v>
@@ -4850,10 +4850,10 @@
     </row>
     <row r="151" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
+        <v>324</v>
+      </c>
+      <c r="C151" t="s">
         <v>325</v>
-      </c>
-      <c r="C151" t="s">
-        <v>326</v>
       </c>
       <c r="D151" t="s">
         <v>1</v>
@@ -4867,13 +4867,13 @@
     </row>
     <row r="152" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
+        <v>326</v>
+      </c>
+      <c r="C152" t="s">
         <v>327</v>
       </c>
-      <c r="C152" t="s">
-        <v>328</v>
-      </c>
       <c r="D152" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E152" t="s">
         <v>15</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="153" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
+        <v>328</v>
+      </c>
+      <c r="C153" t="s">
         <v>329</v>
-      </c>
-      <c r="C153" t="s">
-        <v>330</v>
       </c>
       <c r="D153" t="s">
         <v>18</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="154" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
+        <v>330</v>
+      </c>
+      <c r="C154" t="s">
         <v>331</v>
-      </c>
-      <c r="C154" t="s">
-        <v>332</v>
       </c>
       <c r="D154" t="s">
         <v>4</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
+        <v>332</v>
+      </c>
+      <c r="C155" t="s">
         <v>333</v>
-      </c>
-      <c r="C155" t="s">
-        <v>334</v>
       </c>
       <c r="D155" t="s">
         <v>4</v>
@@ -4935,10 +4935,10 @@
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
+        <v>334</v>
+      </c>
+      <c r="C156" t="s">
         <v>335</v>
-      </c>
-      <c r="C156" t="s">
-        <v>336</v>
       </c>
       <c r="D156" t="s">
         <v>4</v>
@@ -4952,10 +4952,10 @@
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
+        <v>336</v>
+      </c>
+      <c r="C157" t="s">
         <v>337</v>
-      </c>
-      <c r="C157" t="s">
-        <v>338</v>
       </c>
       <c r="D157" t="s">
         <v>4</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="158" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
+        <v>338</v>
+      </c>
+      <c r="C158" t="s">
         <v>339</v>
-      </c>
-      <c r="C158" t="s">
-        <v>340</v>
       </c>
       <c r="D158" t="s">
         <v>18</v>
@@ -4989,10 +4989,10 @@
     </row>
     <row r="159" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
+        <v>340</v>
+      </c>
+      <c r="C159" t="s">
         <v>341</v>
-      </c>
-      <c r="C159" t="s">
-        <v>342</v>
       </c>
       <c r="D159" t="s">
         <v>4</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
+        <v>342</v>
+      </c>
+      <c r="C161" t="s">
         <v>343</v>
       </c>
-      <c r="C161" t="s">
-        <v>344</v>
-      </c>
       <c r="D161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E161" t="s">
         <v>15</v>
@@ -5028,10 +5028,10 @@
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
+        <v>344</v>
+      </c>
+      <c r="C162" t="s">
         <v>345</v>
-      </c>
-      <c r="C162" t="s">
-        <v>346</v>
       </c>
       <c r="D162" t="s">
         <v>18</v>
@@ -5045,13 +5045,13 @@
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
+        <v>346</v>
+      </c>
+      <c r="C163" t="s">
         <v>347</v>
       </c>
-      <c r="C163" t="s">
-        <v>348</v>
-      </c>
       <c r="D163" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E163" t="s">
         <v>15</v>
@@ -5062,10 +5062,10 @@
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
+        <v>348</v>
+      </c>
+      <c r="C164" t="s">
         <v>349</v>
-      </c>
-      <c r="C164" t="s">
-        <v>350</v>
       </c>
       <c r="D164" t="s">
         <v>4</v>
@@ -5079,13 +5079,13 @@
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
+        <v>350</v>
+      </c>
+      <c r="C165" t="s">
         <v>351</v>
       </c>
-      <c r="C165" t="s">
-        <v>352</v>
-      </c>
       <c r="D165" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E165" t="s">
         <v>15</v>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
+        <v>352</v>
+      </c>
+      <c r="C167" t="s">
         <v>353</v>
-      </c>
-      <c r="C167" t="s">
-        <v>354</v>
       </c>
       <c r="D167" t="s">
         <v>19</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
+        <v>354</v>
+      </c>
+      <c r="C168" t="s">
         <v>355</v>
-      </c>
-      <c r="C168" t="s">
-        <v>356</v>
       </c>
       <c r="D168" t="s">
         <v>19</v>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
+        <v>356</v>
+      </c>
+      <c r="C169" t="s">
         <v>357</v>
-      </c>
-      <c r="C169" t="s">
-        <v>358</v>
       </c>
       <c r="D169" t="s">
         <v>19</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
+        <v>358</v>
+      </c>
+      <c r="C170" t="s">
         <v>359</v>
-      </c>
-      <c r="C170" t="s">
-        <v>360</v>
       </c>
       <c r="D170" t="s">
         <v>19</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
+        <v>360</v>
+      </c>
+      <c r="C171" t="s">
         <v>361</v>
-      </c>
-      <c r="C171" t="s">
-        <v>362</v>
       </c>
       <c r="D171" t="s">
         <v>19</v>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
+        <v>362</v>
+      </c>
+      <c r="C173" t="s">
         <v>363</v>
-      </c>
-      <c r="C173" t="s">
-        <v>364</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
+        <v>364</v>
+      </c>
+      <c r="C174" t="s">
         <v>365</v>
-      </c>
-      <c r="C174" t="s">
-        <v>366</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -5225,10 +5225,10 @@
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
+        <v>366</v>
+      </c>
+      <c r="C175" t="s">
         <v>367</v>
-      </c>
-      <c r="C175" t="s">
-        <v>368</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -5242,10 +5242,10 @@
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
+        <v>368</v>
+      </c>
+      <c r="C176" t="s">
         <v>369</v>
-      </c>
-      <c r="C176" t="s">
-        <v>370</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -5259,10 +5259,10 @@
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
+        <v>370</v>
+      </c>
+      <c r="C177" t="s">
         <v>371</v>
-      </c>
-      <c r="C177" t="s">
-        <v>372</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
+        <v>372</v>
+      </c>
+      <c r="C178" t="s">
         <v>373</v>
-      </c>
-      <c r="C178" t="s">
-        <v>374</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
+        <v>374</v>
+      </c>
+      <c r="C179" t="s">
         <v>375</v>
-      </c>
-      <c r="C179" t="s">
-        <v>376</v>
       </c>
       <c r="D179" t="s">
         <v>17</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
+        <v>376</v>
+      </c>
+      <c r="C180" t="s">
         <v>377</v>
-      </c>
-      <c r="C180" t="s">
-        <v>378</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
+        <v>378</v>
+      </c>
+      <c r="C181" t="s">
         <v>379</v>
-      </c>
-      <c r="C181" t="s">
-        <v>380</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
+        <v>380</v>
+      </c>
+      <c r="C182" t="s">
         <v>381</v>
-      </c>
-      <c r="C182" t="s">
-        <v>382</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C184" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D184" t="s">
         <v>4</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
+        <v>383</v>
+      </c>
+      <c r="C185" t="s">
         <v>384</v>
-      </c>
-      <c r="C185" t="s">
-        <v>385</v>
       </c>
       <c r="D185" t="s">
         <v>4</v>
@@ -5400,10 +5400,10 @@
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
+        <v>385</v>
+      </c>
+      <c r="C186" t="s">
         <v>386</v>
-      </c>
-      <c r="C186" t="s">
-        <v>387</v>
       </c>
       <c r="D186" t="s">
         <v>4</v>
@@ -5417,10 +5417,10 @@
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
+        <v>387</v>
+      </c>
+      <c r="C187" t="s">
         <v>388</v>
-      </c>
-      <c r="C187" t="s">
-        <v>389</v>
       </c>
       <c r="D187" t="s">
         <v>4</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
+        <v>389</v>
+      </c>
+      <c r="C188" t="s">
         <v>390</v>
-      </c>
-      <c r="C188" t="s">
-        <v>391</v>
       </c>
       <c r="D188" t="s">
         <v>4</v>
@@ -5451,10 +5451,10 @@
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
+        <v>391</v>
+      </c>
+      <c r="C189" t="s">
         <v>392</v>
-      </c>
-      <c r="C189" t="s">
-        <v>393</v>
       </c>
       <c r="D189" t="s">
         <v>4</v>
@@ -5468,10 +5468,10 @@
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
+        <v>393</v>
+      </c>
+      <c r="C190" t="s">
         <v>394</v>
-      </c>
-      <c r="C190" t="s">
-        <v>395</v>
       </c>
       <c r="D190" t="s">
         <v>4</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
+        <v>395</v>
+      </c>
+      <c r="C191" t="s">
         <v>396</v>
-      </c>
-      <c r="C191" t="s">
-        <v>397</v>
       </c>
       <c r="D191" t="s">
         <v>4</v>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
+        <v>397</v>
+      </c>
+      <c r="C192" t="s">
         <v>398</v>
-      </c>
-      <c r="C192" t="s">
-        <v>399</v>
       </c>
       <c r="D192" t="s">
         <v>4</v>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
+        <v>399</v>
+      </c>
+      <c r="C193" t="s">
         <v>400</v>
-      </c>
-      <c r="C193" t="s">
-        <v>401</v>
       </c>
       <c r="D193" t="s">
         <v>4</v>
@@ -5534,7 +5534,7 @@
         <v>46067</v>
       </c>
       <c r="G193" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.25">
@@ -5544,10 +5544,10 @@
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
+        <v>401</v>
+      </c>
+      <c r="C195" t="s">
         <v>402</v>
-      </c>
-      <c r="C195" t="s">
-        <v>403</v>
       </c>
       <c r="D195" t="s">
         <v>4</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
+        <v>403</v>
+      </c>
+      <c r="C196" t="s">
         <v>404</v>
-      </c>
-      <c r="C196" t="s">
-        <v>405</v>
       </c>
       <c r="D196" t="s">
         <v>4</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="197" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
+        <v>405</v>
+      </c>
+      <c r="C197" t="s">
         <v>406</v>
-      </c>
-      <c r="C197" t="s">
-        <v>407</v>
       </c>
       <c r="D197" t="s">
         <v>4</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
+        <v>407</v>
+      </c>
+      <c r="C198" t="s">
         <v>408</v>
-      </c>
-      <c r="C198" t="s">
-        <v>409</v>
       </c>
       <c r="D198" t="s">
         <v>4</v>
@@ -5612,10 +5612,10 @@
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
+        <v>409</v>
+      </c>
+      <c r="C199" t="s">
         <v>410</v>
-      </c>
-      <c r="C199" t="s">
-        <v>411</v>
       </c>
       <c r="D199" t="s">
         <v>4</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
+        <v>411</v>
+      </c>
+      <c r="C200" t="s">
         <v>412</v>
-      </c>
-      <c r="C200" t="s">
-        <v>413</v>
       </c>
       <c r="D200" t="s">
         <v>4</v>
@@ -5646,10 +5646,10 @@
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C201" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D201" t="s">
         <v>4</v>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C202" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D202" t="s">
         <v>4</v>
@@ -5680,10 +5680,10 @@
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D203" t="s">
         <v>4</v>
@@ -5697,13 +5697,13 @@
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
+        <v>417</v>
+      </c>
+      <c r="C204" t="s">
         <v>418</v>
       </c>
-      <c r="C204" t="s">
-        <v>419</v>
-      </c>
       <c r="D204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E204" t="s">
         <v>15</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
+        <v>419</v>
+      </c>
+      <c r="C206" t="s">
         <v>420</v>
-      </c>
-      <c r="C206" t="s">
-        <v>421</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
+        <v>421</v>
+      </c>
+      <c r="C207" t="s">
         <v>422</v>
-      </c>
-      <c r="C207" t="s">
-        <v>423</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
+        <v>423</v>
+      </c>
+      <c r="C208" t="s">
         <v>424</v>
-      </c>
-      <c r="C208" t="s">
-        <v>425</v>
       </c>
       <c r="D208" t="s">
         <v>18</v>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
+        <v>425</v>
+      </c>
+      <c r="C209" t="s">
         <v>426</v>
-      </c>
-      <c r="C209" t="s">
-        <v>427</v>
       </c>
       <c r="D209" t="s">
         <v>6</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
+        <v>427</v>
+      </c>
+      <c r="C210" t="s">
         <v>428</v>
-      </c>
-      <c r="C210" t="s">
-        <v>429</v>
       </c>
       <c r="D210" t="s">
         <v>6</v>
@@ -5804,10 +5804,10 @@
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
+        <v>429</v>
+      </c>
+      <c r="C211" t="s">
         <v>430</v>
-      </c>
-      <c r="C211" t="s">
-        <v>431</v>
       </c>
       <c r="D211" t="s">
         <v>6</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
+        <v>431</v>
+      </c>
+      <c r="C212" t="s">
         <v>432</v>
-      </c>
-      <c r="C212" t="s">
-        <v>433</v>
       </c>
       <c r="D212" t="s">
         <v>1</v>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
+        <v>433</v>
+      </c>
+      <c r="C213" t="s">
         <v>434</v>
-      </c>
-      <c r="C213" t="s">
-        <v>435</v>
       </c>
       <c r="D213" t="s">
         <v>6</v>
@@ -5855,13 +5855,13 @@
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
+        <v>435</v>
+      </c>
+      <c r="C214" t="s">
         <v>436</v>
       </c>
-      <c r="C214" t="s">
-        <v>437</v>
-      </c>
       <c r="D214" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -5872,10 +5872,10 @@
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
+        <v>437</v>
+      </c>
+      <c r="C215" t="s">
         <v>438</v>
-      </c>
-      <c r="C215" t="s">
-        <v>439</v>
       </c>
       <c r="D215" t="s">
         <v>4</v>
@@ -5894,10 +5894,10 @@
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
+        <v>439</v>
+      </c>
+      <c r="C217" t="s">
         <v>440</v>
-      </c>
-      <c r="C217" t="s">
-        <v>441</v>
       </c>
       <c r="D217" t="s">
         <v>1</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
+        <v>441</v>
+      </c>
+      <c r="C218" t="s">
         <v>442</v>
-      </c>
-      <c r="C218" t="s">
-        <v>443</v>
       </c>
       <c r="D218" t="s">
         <v>9</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
+        <v>443</v>
+      </c>
+      <c r="C219" t="s">
         <v>444</v>
-      </c>
-      <c r="C219" t="s">
-        <v>445</v>
       </c>
       <c r="D219" t="s">
         <v>17</v>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
+        <v>445</v>
+      </c>
+      <c r="C220" t="s">
         <v>446</v>
-      </c>
-      <c r="C220" t="s">
-        <v>447</v>
       </c>
       <c r="D220" t="s">
         <v>6</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
+        <v>447</v>
+      </c>
+      <c r="C221" t="s">
         <v>448</v>
-      </c>
-      <c r="C221" t="s">
-        <v>449</v>
       </c>
       <c r="D221" t="s">
         <v>6</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
+        <v>449</v>
+      </c>
+      <c r="C222" t="s">
         <v>450</v>
-      </c>
-      <c r="C222" t="s">
-        <v>451</v>
       </c>
       <c r="D222" t="s">
         <v>17</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
+        <v>451</v>
+      </c>
+      <c r="C223" t="s">
         <v>452</v>
-      </c>
-      <c r="C223" t="s">
-        <v>453</v>
       </c>
       <c r="D223" t="s">
         <v>17</v>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
+        <v>453</v>
+      </c>
+      <c r="C224" t="s">
         <v>454</v>
-      </c>
-      <c r="C224" t="s">
-        <v>455</v>
       </c>
       <c r="D224" t="s">
         <v>6</v>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
+        <v>455</v>
+      </c>
+      <c r="C225" t="s">
         <v>456</v>
       </c>
-      <c r="C225" t="s">
-        <v>457</v>
-      </c>
       <c r="D225" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E225" t="s">
         <v>15</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="226" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
+        <v>457</v>
+      </c>
+      <c r="C226" t="s">
         <v>458</v>
-      </c>
-      <c r="C226" t="s">
-        <v>459</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
@@ -6069,10 +6069,10 @@
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
+        <v>459</v>
+      </c>
+      <c r="C228" t="s">
         <v>460</v>
-      </c>
-      <c r="C228" t="s">
-        <v>461</v>
       </c>
       <c r="D228" t="s">
         <v>8</v>
@@ -6086,13 +6086,13 @@
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
+        <v>461</v>
+      </c>
+      <c r="C229" t="s">
         <v>462</v>
       </c>
-      <c r="C229" t="s">
-        <v>463</v>
-      </c>
       <c r="D229" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E229" t="s">
         <v>15</v>
@@ -6103,10 +6103,10 @@
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
+        <v>463</v>
+      </c>
+      <c r="C230" t="s">
         <v>464</v>
-      </c>
-      <c r="C230" t="s">
-        <v>465</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -6120,10 +6120,10 @@
     </row>
     <row r="231" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
+        <v>465</v>
+      </c>
+      <c r="C231" t="s">
         <v>466</v>
-      </c>
-      <c r="C231" t="s">
-        <v>467</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="232" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
+        <v>467</v>
+      </c>
+      <c r="C232" t="s">
         <v>468</v>
-      </c>
-      <c r="C232" t="s">
-        <v>469</v>
       </c>
       <c r="D232" t="s">
         <v>18</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
+        <v>469</v>
+      </c>
+      <c r="C234" t="s">
         <v>470</v>
-      </c>
-      <c r="C234" t="s">
-        <v>471</v>
       </c>
       <c r="D234" t="s">
         <v>4</v>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="235" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
+        <v>471</v>
+      </c>
+      <c r="C235" t="s">
         <v>472</v>
-      </c>
-      <c r="C235" t="s">
-        <v>473</v>
       </c>
       <c r="D235" t="s">
         <v>4</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="236" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C236" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D236" t="s">
         <v>4</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="237" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C237" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D237" t="s">
         <v>4</v>
@@ -6227,10 +6227,10 @@
     </row>
     <row r="238" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
+        <v>475</v>
+      </c>
+      <c r="C238" t="s">
         <v>476</v>
-      </c>
-      <c r="C238" t="s">
-        <v>477</v>
       </c>
       <c r="D238" t="s">
         <v>4</v>
@@ -6242,7 +6242,7 @@
         <v>46068</v>
       </c>
       <c r="G238" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="239" spans="2:7" x14ac:dyDescent="0.25">
@@ -6252,10 +6252,10 @@
     </row>
     <row r="240" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" t="s">
         <v>478</v>
-      </c>
-      <c r="C240" t="s">
-        <v>479</v>
       </c>
       <c r="D240" t="s">
         <v>8</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="241" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
+        <v>479</v>
+      </c>
+      <c r="C241" t="s">
         <v>480</v>
-      </c>
-      <c r="C241" t="s">
-        <v>481</v>
       </c>
       <c r="D241" t="s">
         <v>8</v>
@@ -6286,10 +6286,10 @@
     </row>
     <row r="242" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
+        <v>481</v>
+      </c>
+      <c r="C242" t="s">
         <v>482</v>
-      </c>
-      <c r="C242" t="s">
-        <v>483</v>
       </c>
       <c r="D242" t="s">
         <v>8</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="243" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
+        <v>483</v>
+      </c>
+      <c r="C243" t="s">
         <v>484</v>
-      </c>
-      <c r="C243" t="s">
-        <v>485</v>
       </c>
       <c r="D243" t="s">
         <v>8</v>
@@ -6320,10 +6320,10 @@
     </row>
     <row r="244" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
+        <v>485</v>
+      </c>
+      <c r="C244" t="s">
         <v>486</v>
-      </c>
-      <c r="C244" t="s">
-        <v>487</v>
       </c>
       <c r="D244" t="s">
         <v>8</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
+        <v>487</v>
+      </c>
+      <c r="C246" t="s">
         <v>488</v>
-      </c>
-      <c r="C246" t="s">
-        <v>489</v>
       </c>
       <c r="D246" t="s">
         <v>6</v>
@@ -6359,10 +6359,10 @@
     </row>
     <row r="247" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
+        <v>489</v>
+      </c>
+      <c r="C247" t="s">
         <v>490</v>
-      </c>
-      <c r="C247" t="s">
-        <v>491</v>
       </c>
       <c r="D247" t="s">
         <v>18</v>
@@ -6376,10 +6376,10 @@
     </row>
     <row r="248" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
+        <v>491</v>
+      </c>
+      <c r="C248" t="s">
         <v>492</v>
-      </c>
-      <c r="C248" t="s">
-        <v>493</v>
       </c>
       <c r="D248" t="s">
         <v>6</v>
@@ -6393,10 +6393,10 @@
     </row>
     <row r="249" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
+        <v>493</v>
+      </c>
+      <c r="C249" t="s">
         <v>494</v>
-      </c>
-      <c r="C249" t="s">
-        <v>495</v>
       </c>
       <c r="D249" t="s">
         <v>18</v>
@@ -6410,22 +6410,22 @@
     </row>
     <row r="250" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B250" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C250" t="s">
         <v>496</v>
       </c>
-      <c r="C250" t="s">
-        <v>497</v>
-      </c>
       <c r="D250" t="s">
         <v>4</v>
       </c>
       <c r="E250" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F250" s="2">
         <v>46069</v>
       </c>
       <c r="G250" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="251" spans="2:7" x14ac:dyDescent="0.25">
@@ -6435,13 +6435,13 @@
     </row>
     <row r="252" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
+        <v>497</v>
+      </c>
+      <c r="C252" t="s">
         <v>498</v>
       </c>
-      <c r="C252" t="s">
-        <v>499</v>
-      </c>
       <c r="D252" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E252" t="s">
         <v>15</v>
@@ -6452,13 +6452,13 @@
     </row>
     <row r="253" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
+        <v>499</v>
+      </c>
+      <c r="C253" t="s">
         <v>500</v>
       </c>
-      <c r="C253" t="s">
-        <v>501</v>
-      </c>
       <c r="D253" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E253" t="s">
         <v>15</v>
@@ -6469,13 +6469,13 @@
     </row>
     <row r="254" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
+        <v>501</v>
+      </c>
+      <c r="C254" t="s">
         <v>502</v>
       </c>
-      <c r="C254" t="s">
-        <v>503</v>
-      </c>
       <c r="D254" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E254" t="s">
         <v>15</v>
@@ -6486,13 +6486,13 @@
     </row>
     <row r="255" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
+        <v>503</v>
+      </c>
+      <c r="C255" t="s">
         <v>504</v>
       </c>
-      <c r="C255" t="s">
-        <v>505</v>
-      </c>
       <c r="D255" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E255" t="s">
         <v>15</v>
@@ -6503,13 +6503,13 @@
     </row>
     <row r="256" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
+        <v>505</v>
+      </c>
+      <c r="C256" t="s">
         <v>506</v>
       </c>
-      <c r="C256" t="s">
-        <v>507</v>
-      </c>
       <c r="D256" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E256" t="s">
         <v>15</v>
@@ -6525,10 +6525,10 @@
     </row>
     <row r="258" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
+        <v>507</v>
+      </c>
+      <c r="C258" t="s">
         <v>508</v>
-      </c>
-      <c r="C258" t="s">
-        <v>509</v>
       </c>
       <c r="D258" t="s">
         <v>18</v>
@@ -6542,27 +6542,27 @@
     </row>
     <row r="259" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B259" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C259" t="s">
         <v>510</v>
-      </c>
-      <c r="C259" t="s">
-        <v>511</v>
       </c>
       <c r="D259" t="s">
         <v>6</v>
       </c>
       <c r="E259" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G259" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="260" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
+        <v>511</v>
+      </c>
+      <c r="C260" t="s">
         <v>512</v>
-      </c>
-      <c r="C260" t="s">
-        <v>513</v>
       </c>
       <c r="D260" t="s">
         <v>6</v>
@@ -6576,10 +6576,10 @@
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
+        <v>513</v>
+      </c>
+      <c r="C261" t="s">
         <v>514</v>
-      </c>
-      <c r="C261" t="s">
-        <v>515</v>
       </c>
       <c r="D261" t="s">
         <v>4</v>
@@ -6593,10 +6593,10 @@
     </row>
     <row r="262" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
+        <v>515</v>
+      </c>
+      <c r="C262" t="s">
         <v>516</v>
-      </c>
-      <c r="C262" t="s">
-        <v>517</v>
       </c>
       <c r="D262" t="s">
         <v>6</v>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="264" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
+        <v>517</v>
+      </c>
+      <c r="C264" t="s">
         <v>518</v>
-      </c>
-      <c r="C264" t="s">
-        <v>519</v>
       </c>
       <c r="D264" t="s">
         <v>4</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="265" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
+        <v>519</v>
+      </c>
+      <c r="C265" t="s">
         <v>520</v>
-      </c>
-      <c r="C265" t="s">
-        <v>521</v>
       </c>
       <c r="D265" t="s">
         <v>4</v>
@@ -6649,10 +6649,10 @@
     </row>
     <row r="266" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
+        <v>521</v>
+      </c>
+      <c r="C266" t="s">
         <v>522</v>
-      </c>
-      <c r="C266" t="s">
-        <v>523</v>
       </c>
       <c r="D266" t="s">
         <v>4</v>
@@ -6666,10 +6666,10 @@
     </row>
     <row r="267" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
+        <v>523</v>
+      </c>
+      <c r="C267" t="s">
         <v>524</v>
-      </c>
-      <c r="C267" t="s">
-        <v>525</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
@@ -6683,10 +6683,10 @@
     </row>
     <row r="268" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
+        <v>525</v>
+      </c>
+      <c r="C268" t="s">
         <v>526</v>
-      </c>
-      <c r="C268" t="s">
-        <v>527</v>
       </c>
       <c r="D268" t="s">
         <v>4</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="270" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
+        <v>527</v>
+      </c>
+      <c r="C270" t="s">
         <v>528</v>
-      </c>
-      <c r="C270" t="s">
-        <v>529</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -6722,10 +6722,10 @@
     </row>
     <row r="271" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
+        <v>529</v>
+      </c>
+      <c r="C271" t="s">
         <v>530</v>
-      </c>
-      <c r="C271" t="s">
-        <v>531</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -6739,10 +6739,10 @@
     </row>
     <row r="272" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
+        <v>531</v>
+      </c>
+      <c r="C272" t="s">
         <v>532</v>
-      </c>
-      <c r="C272" t="s">
-        <v>533</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -6756,10 +6756,10 @@
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
+        <v>533</v>
+      </c>
+      <c r="C273" t="s">
         <v>534</v>
-      </c>
-      <c r="C273" t="s">
-        <v>535</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -6773,10 +6773,10 @@
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
+        <v>535</v>
+      </c>
+      <c r="C274" t="s">
         <v>536</v>
-      </c>
-      <c r="C274" t="s">
-        <v>537</v>
       </c>
       <c r="D274" t="s">
         <v>2</v>
@@ -6793,77 +6793,77 @@
         <v>55</v>
       </c>
       <c r="E275" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
+        <v>537</v>
+      </c>
+      <c r="C276" t="s">
         <v>538</v>
-      </c>
-      <c r="C276" t="s">
-        <v>539</v>
       </c>
       <c r="D276" t="s">
         <v>19</v>
       </c>
       <c r="E276" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
+        <v>539</v>
+      </c>
+      <c r="C277" t="s">
         <v>540</v>
-      </c>
-      <c r="C277" t="s">
-        <v>541</v>
       </c>
       <c r="D277" t="s">
         <v>19</v>
       </c>
       <c r="E277" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
+        <v>541</v>
+      </c>
+      <c r="C278" t="s">
         <v>542</v>
-      </c>
-      <c r="C278" t="s">
-        <v>543</v>
       </c>
       <c r="D278" t="s">
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
+        <v>543</v>
+      </c>
+      <c r="C279" t="s">
         <v>544</v>
-      </c>
-      <c r="C279" t="s">
-        <v>545</v>
       </c>
       <c r="D279" t="s">
         <v>19</v>
       </c>
       <c r="E279" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
+        <v>545</v>
+      </c>
+      <c r="C280" t="s">
         <v>546</v>
-      </c>
-      <c r="C280" t="s">
-        <v>547</v>
       </c>
       <c r="D280" t="s">
         <v>19</v>
       </c>
       <c r="E280" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.25">
@@ -6871,77 +6871,77 @@
         <v>56</v>
       </c>
       <c r="E281" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
+        <v>547</v>
+      </c>
+      <c r="C282" t="s">
         <v>548</v>
-      </c>
-      <c r="C282" t="s">
-        <v>549</v>
       </c>
       <c r="D282" t="s">
         <v>6</v>
       </c>
       <c r="E282" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
+        <v>549</v>
+      </c>
+      <c r="C283" t="s">
         <v>550</v>
-      </c>
-      <c r="C283" t="s">
-        <v>551</v>
       </c>
       <c r="D283" t="s">
         <v>6</v>
       </c>
       <c r="E283" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
+        <v>551</v>
+      </c>
+      <c r="C284" t="s">
         <v>552</v>
-      </c>
-      <c r="C284" t="s">
-        <v>553</v>
       </c>
       <c r="D284" t="s">
         <v>6</v>
       </c>
       <c r="E284" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
+        <v>553</v>
+      </c>
+      <c r="C285" t="s">
         <v>554</v>
-      </c>
-      <c r="C285" t="s">
-        <v>555</v>
       </c>
       <c r="D285" t="s">
         <v>6</v>
       </c>
       <c r="E285" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
+        <v>555</v>
+      </c>
+      <c r="C286" t="s">
         <v>556</v>
-      </c>
-      <c r="C286" t="s">
-        <v>557</v>
       </c>
       <c r="D286" t="s">
         <v>6</v>
       </c>
       <c r="E286" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.25">
@@ -6949,77 +6949,77 @@
         <v>57</v>
       </c>
       <c r="E287" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
+        <v>557</v>
+      </c>
+      <c r="C288" t="s">
         <v>558</v>
       </c>
-      <c r="C288" t="s">
-        <v>559</v>
-      </c>
       <c r="D288" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E288" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
+        <v>559</v>
+      </c>
+      <c r="C289" t="s">
         <v>560</v>
-      </c>
-      <c r="C289" t="s">
-        <v>561</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
       </c>
       <c r="E289" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
+        <v>561</v>
+      </c>
+      <c r="C290" t="s">
         <v>562</v>
-      </c>
-      <c r="C290" t="s">
-        <v>563</v>
       </c>
       <c r="D290" t="s">
         <v>17</v>
       </c>
       <c r="E290" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
+        <v>563</v>
+      </c>
+      <c r="C291" t="s">
         <v>564</v>
       </c>
-      <c r="C291" t="s">
+      <c r="D291" t="s">
         <v>565</v>
       </c>
-      <c r="D291" t="s">
-        <v>566</v>
-      </c>
       <c r="E291" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
+        <v>566</v>
+      </c>
+      <c r="C292" t="s">
         <v>567</v>
       </c>
-      <c r="C292" t="s">
-        <v>568</v>
-      </c>
       <c r="D292" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E292" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.25">
@@ -7027,77 +7027,77 @@
         <v>58</v>
       </c>
       <c r="E293" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
+        <v>568</v>
+      </c>
+      <c r="C294" t="s">
         <v>569</v>
-      </c>
-      <c r="C294" t="s">
-        <v>570</v>
       </c>
       <c r="D294" t="s">
         <v>6</v>
       </c>
       <c r="E294" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
+        <v>570</v>
+      </c>
+      <c r="C295" t="s">
         <v>571</v>
-      </c>
-      <c r="C295" t="s">
-        <v>572</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
       </c>
       <c r="E295" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
+        <v>572</v>
+      </c>
+      <c r="C296" t="s">
         <v>573</v>
       </c>
-      <c r="C296" t="s">
-        <v>574</v>
-      </c>
       <c r="D296" t="s">
         <v>4</v>
       </c>
       <c r="E296" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
+        <v>574</v>
+      </c>
+      <c r="C297" t="s">
         <v>575</v>
-      </c>
-      <c r="C297" t="s">
-        <v>576</v>
       </c>
       <c r="D297" t="s">
         <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
+        <v>576</v>
+      </c>
+      <c r="C298" t="s">
         <v>577</v>
       </c>
-      <c r="C298" t="s">
-        <v>578</v>
-      </c>
       <c r="D298" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E298" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.25">
@@ -7105,77 +7105,77 @@
         <v>59</v>
       </c>
       <c r="E299" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
+        <v>578</v>
+      </c>
+      <c r="C300" t="s">
         <v>579</v>
-      </c>
-      <c r="C300" t="s">
-        <v>580</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
       </c>
       <c r="E300" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
+        <v>580</v>
+      </c>
+      <c r="C301" t="s">
         <v>581</v>
-      </c>
-      <c r="C301" t="s">
-        <v>582</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
       </c>
       <c r="E301" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
+        <v>582</v>
+      </c>
+      <c r="C302" t="s">
         <v>583</v>
-      </c>
-      <c r="C302" t="s">
-        <v>584</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
       </c>
       <c r="E302" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
+        <v>584</v>
+      </c>
+      <c r="C303" t="s">
         <v>585</v>
-      </c>
-      <c r="C303" t="s">
-        <v>586</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
       </c>
       <c r="E303" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
+        <v>586</v>
+      </c>
+      <c r="C304" t="s">
         <v>587</v>
       </c>
-      <c r="C304" t="s">
-        <v>588</v>
-      </c>
       <c r="D304" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E304" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.25">
@@ -7183,77 +7183,77 @@
         <v>60</v>
       </c>
       <c r="E305" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
+        <v>588</v>
+      </c>
+      <c r="C306" t="s">
         <v>589</v>
-      </c>
-      <c r="C306" t="s">
-        <v>590</v>
       </c>
       <c r="D306" t="s">
         <v>19</v>
       </c>
       <c r="E306" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
+        <v>590</v>
+      </c>
+      <c r="C307" t="s">
         <v>591</v>
-      </c>
-      <c r="C307" t="s">
-        <v>592</v>
       </c>
       <c r="D307" t="s">
         <v>19</v>
       </c>
       <c r="E307" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
+        <v>592</v>
+      </c>
+      <c r="C308" t="s">
         <v>593</v>
-      </c>
-      <c r="C308" t="s">
-        <v>594</v>
       </c>
       <c r="D308" t="s">
         <v>19</v>
       </c>
       <c r="E308" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
+        <v>594</v>
+      </c>
+      <c r="C309" t="s">
         <v>595</v>
-      </c>
-      <c r="C309" t="s">
-        <v>596</v>
       </c>
       <c r="D309" t="s">
         <v>19</v>
       </c>
       <c r="E309" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
+        <v>596</v>
+      </c>
+      <c r="C310" t="s">
         <v>597</v>
-      </c>
-      <c r="C310" t="s">
-        <v>598</v>
       </c>
       <c r="D310" t="s">
         <v>19</v>
       </c>
       <c r="E310" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.25">
@@ -7261,147 +7261,147 @@
         <v>61</v>
       </c>
       <c r="E311" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
+        <v>598</v>
+      </c>
+      <c r="C312" t="s">
         <v>599</v>
-      </c>
-      <c r="C312" t="s">
-        <v>600</v>
       </c>
       <c r="D312" t="s">
         <v>18</v>
       </c>
       <c r="E312" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
+        <v>600</v>
+      </c>
+      <c r="C313" t="s">
         <v>601</v>
       </c>
-      <c r="C313" t="s">
-        <v>602</v>
-      </c>
       <c r="D313" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E313" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
+        <v>602</v>
+      </c>
+      <c r="C314" t="s">
         <v>603</v>
-      </c>
-      <c r="C314" t="s">
-        <v>604</v>
       </c>
       <c r="D314" t="s">
         <v>6</v>
       </c>
       <c r="E314" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
+        <v>604</v>
+      </c>
+      <c r="C315" t="s">
         <v>605</v>
-      </c>
-      <c r="C315" t="s">
-        <v>606</v>
       </c>
       <c r="D315" t="s">
         <v>18</v>
       </c>
       <c r="E315" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
+        <v>606</v>
+      </c>
+      <c r="C316" t="s">
         <v>607</v>
       </c>
-      <c r="C316" t="s">
-        <v>608</v>
-      </c>
       <c r="D316" t="s">
         <v>4</v>
       </c>
       <c r="E316" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
+        <v>608</v>
+      </c>
+      <c r="C317" t="s">
         <v>609</v>
-      </c>
-      <c r="C317" t="s">
-        <v>610</v>
       </c>
       <c r="D317" t="s">
         <v>18</v>
       </c>
       <c r="E317" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
+        <v>610</v>
+      </c>
+      <c r="C318" t="s">
         <v>611</v>
-      </c>
-      <c r="C318" t="s">
-        <v>612</v>
       </c>
       <c r="D318" t="s">
         <v>6</v>
       </c>
       <c r="E318" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
+        <v>612</v>
+      </c>
+      <c r="C319" t="s">
         <v>613</v>
-      </c>
-      <c r="C319" t="s">
-        <v>614</v>
       </c>
       <c r="D319" t="s">
         <v>6</v>
       </c>
       <c r="E319" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
+        <v>614</v>
+      </c>
+      <c r="C320" t="s">
         <v>615</v>
-      </c>
-      <c r="C320" t="s">
-        <v>616</v>
       </c>
       <c r="D320" t="s">
         <v>19</v>
       </c>
       <c r="E320" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
+        <v>616</v>
+      </c>
+      <c r="C321" t="s">
         <v>617</v>
-      </c>
-      <c r="C321" t="s">
-        <v>618</v>
       </c>
       <c r="D321" t="s">
         <v>6</v>
       </c>
       <c r="E321" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.25">
@@ -7409,287 +7409,287 @@
         <v>62</v>
       </c>
       <c r="E322" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" t="s">
+        <v>618</v>
+      </c>
+      <c r="C323" t="s">
         <v>619</v>
       </c>
-      <c r="C323" t="s">
-        <v>620</v>
-      </c>
       <c r="D323" t="s">
         <v>4</v>
       </c>
       <c r="E323" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" t="s">
+        <v>620</v>
+      </c>
+      <c r="C324" t="s">
         <v>621</v>
-      </c>
-      <c r="C324" t="s">
-        <v>622</v>
       </c>
       <c r="D324" t="s">
         <v>17</v>
       </c>
       <c r="E324" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
+        <v>622</v>
+      </c>
+      <c r="C325" t="s">
         <v>623</v>
-      </c>
-      <c r="C325" t="s">
-        <v>624</v>
       </c>
       <c r="D325" t="s">
         <v>9</v>
       </c>
       <c r="E325" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" t="s">
+        <v>624</v>
+      </c>
+      <c r="C326" t="s">
         <v>625</v>
-      </c>
-      <c r="C326" t="s">
-        <v>626</v>
       </c>
       <c r="D326" t="s">
         <v>18</v>
       </c>
       <c r="E326" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" t="s">
+        <v>626</v>
+      </c>
+      <c r="C327" t="s">
         <v>627</v>
       </c>
-      <c r="C327" t="s">
-        <v>628</v>
-      </c>
       <c r="D327" t="s">
         <v>4</v>
       </c>
       <c r="E327" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
+        <v>628</v>
+      </c>
+      <c r="C328" t="s">
         <v>629</v>
       </c>
-      <c r="C328" t="s">
-        <v>630</v>
-      </c>
       <c r="D328" t="s">
         <v>4</v>
       </c>
       <c r="E328" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
+        <v>630</v>
+      </c>
+      <c r="C329" t="s">
         <v>631</v>
       </c>
-      <c r="C329" t="s">
-        <v>632</v>
-      </c>
       <c r="D329" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E329" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" t="s">
+        <v>632</v>
+      </c>
+      <c r="C330" t="s">
         <v>633</v>
       </c>
-      <c r="C330" t="s">
-        <v>634</v>
-      </c>
       <c r="D330" t="s">
         <v>4</v>
       </c>
       <c r="E330" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
+        <v>634</v>
+      </c>
+      <c r="C331" t="s">
         <v>635</v>
-      </c>
-      <c r="C331" t="s">
-        <v>636</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
       </c>
       <c r="E331" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
+        <v>636</v>
+      </c>
+      <c r="C332" t="s">
         <v>637</v>
-      </c>
-      <c r="C332" t="s">
-        <v>638</v>
       </c>
       <c r="D332" t="s">
         <v>6</v>
       </c>
       <c r="E332" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" t="s">
+        <v>638</v>
+      </c>
+      <c r="C333" t="s">
         <v>639</v>
       </c>
-      <c r="C333" t="s">
-        <v>640</v>
-      </c>
       <c r="D333" t="s">
         <v>4</v>
       </c>
       <c r="E333" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
+        <v>640</v>
+      </c>
+      <c r="C334" t="s">
         <v>641</v>
-      </c>
-      <c r="C334" t="s">
-        <v>642</v>
       </c>
       <c r="D334" t="s">
         <v>1</v>
       </c>
       <c r="E334" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" t="s">
+        <v>642</v>
+      </c>
+      <c r="C335" t="s">
         <v>643</v>
-      </c>
-      <c r="C335" t="s">
-        <v>644</v>
       </c>
       <c r="D335" t="s">
         <v>17</v>
       </c>
       <c r="E335" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
+        <v>644</v>
+      </c>
+      <c r="C336" t="s">
         <v>645</v>
       </c>
-      <c r="C336" t="s">
-        <v>646</v>
-      </c>
       <c r="D336" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E336" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
+        <v>646</v>
+      </c>
+      <c r="C337" t="s">
         <v>647</v>
       </c>
-      <c r="C337" t="s">
-        <v>648</v>
-      </c>
       <c r="D337" t="s">
         <v>4</v>
       </c>
       <c r="E337" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
+        <v>648</v>
+      </c>
+      <c r="C338" t="s">
         <v>649</v>
-      </c>
-      <c r="C338" t="s">
-        <v>650</v>
       </c>
       <c r="D338" t="s">
         <v>6</v>
       </c>
       <c r="E338" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
+        <v>650</v>
+      </c>
+      <c r="C339" t="s">
         <v>651</v>
-      </c>
-      <c r="C339" t="s">
-        <v>652</v>
       </c>
       <c r="D339" t="s">
         <v>19</v>
       </c>
       <c r="E339" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
+        <v>652</v>
+      </c>
+      <c r="C340" t="s">
         <v>653</v>
-      </c>
-      <c r="C340" t="s">
-        <v>654</v>
       </c>
       <c r="D340" t="s">
         <v>6</v>
       </c>
       <c r="E340" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
+        <v>654</v>
+      </c>
+      <c r="C341" t="s">
         <v>655</v>
-      </c>
-      <c r="C341" t="s">
-        <v>656</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
       </c>
       <c r="E341" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
+        <v>656</v>
+      </c>
+      <c r="C342" t="s">
         <v>657</v>
-      </c>
-      <c r="C342" t="s">
-        <v>658</v>
       </c>
       <c r="D342" t="s">
         <v>6</v>
       </c>
       <c r="E342" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C771EC6-F31F-46AF-AE24-908C8CDCA34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90837C5A-5435-45B3-97B0-FE6B64DB5B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -3526,7 +3526,7 @@
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F65" s="2">
         <v>46061</v>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F66" s="2">
         <v>46062</v>
@@ -3560,7 +3560,7 @@
         <v>8</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F67" s="2">
         <v>46062</v>
@@ -3577,7 +3577,7 @@
         <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F68" s="2">
         <v>46062</v>
@@ -3599,7 +3599,7 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F70" s="2">
         <v>46062</v>
@@ -3616,7 +3616,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F71" s="2">
         <v>46062</v>
@@ -3633,7 +3633,7 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F72" s="2">
         <v>46062</v>
@@ -3650,7 +3650,7 @@
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F73" s="2">
         <v>46062</v>
@@ -3667,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F74" s="2">
         <v>46062</v>
@@ -3684,7 +3684,7 @@
         <v>193</v>
       </c>
       <c r="E75" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F75" s="2">
         <v>46062</v>
@@ -3701,7 +3701,7 @@
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F76" s="2">
         <v>46062</v>
@@ -3718,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="E77" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F77" s="2">
         <v>46062</v>
@@ -3735,7 +3735,7 @@
         <v>4</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F78" s="2">
         <v>46062</v>
@@ -3752,7 +3752,7 @@
         <v>193</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F79" s="2">
         <v>46062</v>
@@ -3774,7 +3774,7 @@
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F81" s="2">
         <v>46062</v>
@@ -3791,7 +3791,7 @@
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F82" s="2">
         <v>46062</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F83" s="2">
         <v>46062</v>
@@ -3825,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F84" s="2">
         <v>46062</v>
@@ -3842,7 +3842,7 @@
         <v>4</v>
       </c>
       <c r="E85" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F85" s="2">
         <v>46062</v>
@@ -3864,7 +3864,7 @@
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F87" s="2">
         <v>46063</v>
@@ -3881,7 +3881,7 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F88" s="2">
         <v>46063</v>
@@ -3898,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F89" s="2">
         <v>46063</v>
@@ -3915,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F90" s="2">
         <v>46063</v>
@@ -3932,7 +3932,7 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F91" s="2">
         <v>46063</v>
@@ -4137,7 +4137,7 @@
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F105" s="2">
         <v>46063</v>
@@ -4154,7 +4154,7 @@
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F106" s="2">
         <v>46063</v>
@@ -4171,7 +4171,7 @@
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F107" s="2">
         <v>46063</v>
@@ -4188,7 +4188,7 @@
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F108" s="2">
         <v>46063</v>
@@ -4205,7 +4205,7 @@
         <v>7</v>
       </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F109" s="2">
         <v>46063</v>
@@ -4227,7 +4227,7 @@
         <v>17</v>
       </c>
       <c r="E111" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F111" s="2">
         <v>46063</v>
@@ -4244,7 +4244,7 @@
         <v>17</v>
       </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F112" s="2">
         <v>46063</v>
@@ -4261,7 +4261,7 @@
         <v>17</v>
       </c>
       <c r="E113" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F113" s="2">
         <v>46063</v>
@@ -4278,7 +4278,7 @@
         <v>17</v>
       </c>
       <c r="E114" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F114" s="2">
         <v>46063</v>
@@ -4295,7 +4295,7 @@
         <v>17</v>
       </c>
       <c r="E115" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F115" s="2">
         <v>46063</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90837C5A-5435-45B3-97B0-FE6B64DB5B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55138BD-06DC-49CF-A825-96A9096F3C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -4317,7 +4317,7 @@
         <v>4</v>
       </c>
       <c r="E117" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F117" s="2">
         <v>46064</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55138BD-06DC-49CF-A825-96A9096F3C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E92B76B-7031-4C62-B38B-D6E18749C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -4334,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="E118" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F118" s="2">
         <v>46064</v>
@@ -4351,7 +4351,7 @@
         <v>4</v>
       </c>
       <c r="E119" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F119" s="2">
         <v>46064</v>
@@ -4368,7 +4368,7 @@
         <v>4</v>
       </c>
       <c r="E120" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F120" s="2">
         <v>46064</v>
@@ -4385,7 +4385,7 @@
         <v>4</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F121" s="2">
         <v>46064</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E92B76B-7031-4C62-B38B-D6E18749C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3CC6CD-7E7D-4572-A05F-C5ED1436C808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -4402,7 +4402,7 @@
         <v>18</v>
       </c>
       <c r="E122" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F122" s="2">
         <v>46064</v>
@@ -4419,7 +4419,7 @@
         <v>4</v>
       </c>
       <c r="E123" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F123" s="2">
         <v>46064</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3CC6CD-7E7D-4572-A05F-C5ED1436C808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58AC8-BCE2-42A8-A08D-6E65A1212451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -4436,7 +4436,7 @@
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F124" s="2">
         <v>46064</v>
@@ -4453,7 +4453,7 @@
         <v>4</v>
       </c>
       <c r="E125" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F125" s="2">
         <v>46064</v>
@@ -4470,7 +4470,7 @@
         <v>4</v>
       </c>
       <c r="E126" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F126" s="2">
         <v>46064</v>
@@ -4667,7 +4667,7 @@
         <v>7</v>
       </c>
       <c r="E139" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F139" s="2">
         <v>46064</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58AC8-BCE2-42A8-A08D-6E65A1212451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E82AB4E-316F-4020-9160-DE69CCA02E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -4684,7 +4684,7 @@
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F140" s="2">
         <v>46064</v>
@@ -4701,7 +4701,7 @@
         <v>7</v>
       </c>
       <c r="E141" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F141" s="2">
         <v>46065</v>
@@ -4718,7 +4718,7 @@
         <v>7</v>
       </c>
       <c r="E142" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F142" s="2">
         <v>46065</v>
@@ -4735,7 +4735,7 @@
         <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F143" s="2">
         <v>46065</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E82AB4E-316F-4020-9160-DE69CCA02E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E43A188-B255-4BF4-900D-F2000E7AD43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -4752,7 +4752,7 @@
         <v>7</v>
       </c>
       <c r="E144" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F144" s="2">
         <v>46065</v>
@@ -4769,7 +4769,7 @@
         <v>7</v>
       </c>
       <c r="E145" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F145" s="2">
         <v>46065</v>
@@ -4786,7 +4786,7 @@
         <v>17</v>
       </c>
       <c r="E146" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F146" s="2">
         <v>46065</v>
@@ -4803,7 +4803,7 @@
         <v>17</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F147" s="2">
         <v>46065</v>
@@ -4820,7 +4820,7 @@
         <v>7</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F148" s="2">
         <v>46065</v>
@@ -4842,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F150" s="2">
         <v>46065</v>
@@ -4859,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F151" s="2">
         <v>46065</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E43A188-B255-4BF4-900D-F2000E7AD43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1484136F-85DA-44A0-BB1C-40B0F432B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -4876,7 +4876,7 @@
         <v>224</v>
       </c>
       <c r="E152" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F152" s="2">
         <v>46065</v>
@@ -4893,7 +4893,7 @@
         <v>18</v>
       </c>
       <c r="E153" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F153" s="2">
         <v>46065</v>
@@ -4910,7 +4910,7 @@
         <v>4</v>
       </c>
       <c r="E154" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F154" s="2">
         <v>46065</v>
@@ -4927,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F155" s="2">
         <v>46065</v>
@@ -4944,7 +4944,7 @@
         <v>4</v>
       </c>
       <c r="E156" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F156" s="2">
         <v>46065</v>
@@ -4961,7 +4961,7 @@
         <v>4</v>
       </c>
       <c r="E157" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F157" s="2">
         <v>46065</v>
@@ -4981,7 +4981,7 @@
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F158" s="2">
         <v>46065</v>
@@ -4998,7 +4998,7 @@
         <v>4</v>
       </c>
       <c r="E159" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F159" s="2">
         <v>46065</v>
@@ -5200,7 +5200,7 @@
         <v>7</v>
       </c>
       <c r="E173" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F173" s="2">
         <v>46066</v>
@@ -5217,7 +5217,7 @@
         <v>7</v>
       </c>
       <c r="E174" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F174" s="2">
         <v>46066</v>
@@ -5234,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="E175" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F175" s="2">
         <v>46066</v>
@@ -5251,7 +5251,7 @@
         <v>7</v>
       </c>
       <c r="E176" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F176" s="2">
         <v>46066</v>
@@ -5268,7 +5268,7 @@
         <v>7</v>
       </c>
       <c r="E177" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F177" s="2">
         <v>46066</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1484136F-85DA-44A0-BB1C-40B0F432B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D94D1A1-5513-4863-9437-8FAB85AD904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5285,7 +5285,7 @@
         <v>7</v>
       </c>
       <c r="E178" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F178" s="2">
         <v>46066</v>
@@ -5302,7 +5302,7 @@
         <v>17</v>
       </c>
       <c r="E179" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F179" s="2">
         <v>46066</v>
@@ -5319,7 +5319,7 @@
         <v>7</v>
       </c>
       <c r="E180" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F180" s="2">
         <v>46066</v>
@@ -5336,7 +5336,7 @@
         <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F181" s="2">
         <v>46066</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D94D1A1-5513-4863-9437-8FAB85AD904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA398B19-EA8D-47B3-AB86-58C97B2A5059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="570" yWindow="285" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -5353,7 +5353,7 @@
         <v>7</v>
       </c>
       <c r="E182" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F182" s="2">
         <v>46066</v>
@@ -5375,7 +5375,7 @@
         <v>4</v>
       </c>
       <c r="E184" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F184" s="2">
         <v>46066</v>
@@ -5392,7 +5392,7 @@
         <v>4</v>
       </c>
       <c r="E185" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F185" s="2">
         <v>46066</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA398B19-EA8D-47B3-AB86-58C97B2A5059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792EE1D5-31D4-4963-9EB2-5DD4AB61DB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="285" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -5409,7 +5409,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F186" s="2">
         <v>46066</v>
@@ -5426,7 +5426,7 @@
         <v>4</v>
       </c>
       <c r="E187" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F187" s="2">
         <v>46066</v>
@@ -5443,7 +5443,7 @@
         <v>4</v>
       </c>
       <c r="E188" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F188" s="2">
         <v>46066</v>
@@ -5460,7 +5460,7 @@
         <v>4</v>
       </c>
       <c r="E189" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F189" s="2">
         <v>46066</v>
@@ -5477,7 +5477,7 @@
         <v>4</v>
       </c>
       <c r="E190" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F190" s="2">
         <v>46066</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792EE1D5-31D4-4963-9EB2-5DD4AB61DB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C93155B-6899-44A8-8566-8632F035A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5494,7 +5494,7 @@
         <v>4</v>
       </c>
       <c r="E191" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F191" s="2">
         <v>46067</v>
@@ -5511,7 +5511,7 @@
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F192" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C93155B-6899-44A8-8566-8632F035A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5128CB-2F69-4FE6-B13E-F557B571C227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5528,7 +5528,7 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F193" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5128CB-2F69-4FE6-B13E-F557B571C227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2E83A7-24E8-4DAD-8EDD-403E02401F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="930" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -5553,7 +5553,7 @@
         <v>4</v>
       </c>
       <c r="E195" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F195" s="2">
         <v>46067</v>
@@ -5570,7 +5570,7 @@
         <v>4</v>
       </c>
       <c r="E196" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F196" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2E83A7-24E8-4DAD-8EDD-403E02401F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9084BD0E-93AF-407C-93D0-39DD05162974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5587,7 +5587,7 @@
         <v>4</v>
       </c>
       <c r="E197" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F197" s="2">
         <v>46067</v>
@@ -5604,7 +5604,7 @@
         <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F198" s="2">
         <v>46067</v>
@@ -5621,7 +5621,7 @@
         <v>4</v>
       </c>
       <c r="E199" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F199" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9084BD0E-93AF-407C-93D0-39DD05162974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB41B68-1874-4375-850D-A7A333B816F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5638,7 +5638,7 @@
         <v>4</v>
       </c>
       <c r="E200" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F200" s="2">
         <v>46067</v>
@@ -5655,7 +5655,7 @@
         <v>4</v>
       </c>
       <c r="E201" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F201" s="2">
         <v>46067</v>
@@ -5672,7 +5672,7 @@
         <v>4</v>
       </c>
       <c r="E202" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F202" s="2">
         <v>46067</v>
@@ -5689,7 +5689,7 @@
         <v>4</v>
       </c>
       <c r="E203" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F203" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB41B68-1874-4375-850D-A7A333B816F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFE07B8-4383-4667-9278-A4807298EBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1875" yWindow="195" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -5706,7 +5706,7 @@
         <v>193</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F204" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFE07B8-4383-4667-9278-A4807298EBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC3927-C322-415E-AAA8-A01D7CA3504D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="195" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -5728,7 +5728,7 @@
         <v>18</v>
       </c>
       <c r="E206" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F206" s="2">
         <v>46067</v>
@@ -5745,7 +5745,7 @@
         <v>18</v>
       </c>
       <c r="E207" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F207" s="2">
         <v>46067</v>
@@ -5762,7 +5762,7 @@
         <v>18</v>
       </c>
       <c r="E208" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F208" s="2">
         <v>46067</v>
@@ -5779,7 +5779,7 @@
         <v>6</v>
       </c>
       <c r="E209" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F209" s="2">
         <v>46067</v>
@@ -5796,7 +5796,7 @@
         <v>6</v>
       </c>
       <c r="E210" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F210" s="2">
         <v>46067</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC3927-C322-415E-AAA8-A01D7CA3504D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72C1482-5904-47B2-95EB-E1859EA7600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5813,7 +5813,7 @@
         <v>6</v>
       </c>
       <c r="E211" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F211" s="2">
         <v>46067</v>
@@ -5830,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F212" s="2">
         <v>46067</v>
@@ -5847,7 +5847,7 @@
         <v>6</v>
       </c>
       <c r="E213" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F213" s="2">
         <v>46068</v>
@@ -5864,7 +5864,7 @@
         <v>224</v>
       </c>
       <c r="E214" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F214" s="2">
         <v>46068</v>
@@ -5881,7 +5881,7 @@
         <v>4</v>
       </c>
       <c r="E215" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F215" s="2">
         <v>46068</v>
@@ -5903,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F217" s="2">
         <v>46068</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72C1482-5904-47B2-95EB-E1859EA7600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859B0528-7FE5-41EF-BEE5-EFC6310B0271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -5920,7 +5920,7 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F218" s="2">
         <v>46068</v>
@@ -5937,7 +5937,7 @@
         <v>17</v>
       </c>
       <c r="E219" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F219" s="2">
         <v>46068</v>
@@ -5954,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="E220" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F220" s="2">
         <v>46068</v>
@@ -5971,7 +5971,7 @@
         <v>6</v>
       </c>
       <c r="E221" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F221" s="2">
         <v>46068</v>
@@ -5988,7 +5988,7 @@
         <v>17</v>
       </c>
       <c r="E222" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F222" s="2">
         <v>46068</v>
@@ -6005,7 +6005,7 @@
         <v>17</v>
       </c>
       <c r="E223" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F223" s="2">
         <v>46068</v>
@@ -6022,7 +6022,7 @@
         <v>6</v>
       </c>
       <c r="E224" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F224" s="2">
         <v>46068</v>
@@ -6039,7 +6039,7 @@
         <v>224</v>
       </c>
       <c r="E225" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F225" s="2">
         <v>46068</v>
@@ -6056,7 +6056,7 @@
         <v>9</v>
       </c>
       <c r="E226" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F226" s="2">
         <v>46068</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859B0528-7FE5-41EF-BEE5-EFC6310B0271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4966A6BE-B5EC-4747-9C9E-5984A324B5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -6168,7 +6168,7 @@
         <v>4</v>
       </c>
       <c r="E234" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F234" s="2">
         <v>46068</v>
@@ -6185,7 +6185,7 @@
         <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F235" s="2">
         <v>46068</v>
@@ -6202,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="E236" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F236" s="2">
         <v>46068</v>
@@ -6219,14 +6219,14 @@
         <v>4</v>
       </c>
       <c r="E237" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F237" s="2">
         <v>46068</v>
       </c>
     </row>
     <row r="238" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B238" t="s">
+      <c r="B238" s="4" t="s">
         <v>475</v>
       </c>
       <c r="C238" t="s">
@@ -6236,7 +6236,7 @@
         <v>4</v>
       </c>
       <c r="E238" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F238" s="2">
         <v>46068</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4966A6BE-B5EC-4747-9C9E-5984A324B5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17D03E1-9EC0-454C-8CA1-1A2988335382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -2451,6 +2451,7 @@
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
     <col min="2" max="2" width="33.140625" customWidth="1"/>
     <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6261,7 +6262,7 @@
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F240" s="2">
         <v>46069</v>
@@ -6278,7 +6279,7 @@
         <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F241" s="2">
         <v>46069</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17D03E1-9EC0-454C-8CA1-1A2988335382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F7C4EF-A9B5-4BD0-8B18-AC6358781108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -6296,7 +6296,7 @@
         <v>8</v>
       </c>
       <c r="E242" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F242" s="2">
         <v>46069</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F7C4EF-A9B5-4BD0-8B18-AC6358781108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD27F57-7C75-46F5-AE86-95AF2CAC339D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -6313,7 +6313,7 @@
         <v>8</v>
       </c>
       <c r="E243" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F243" s="2">
         <v>46069</v>
@@ -6330,7 +6330,7 @@
         <v>8</v>
       </c>
       <c r="E244" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F244" s="2">
         <v>46069</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD27F57-7C75-46F5-AE86-95AF2CAC339D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0565D286-374F-4355-A9F9-6E1FB8E44D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
@@ -6352,7 +6352,7 @@
         <v>6</v>
       </c>
       <c r="E246" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F246" s="2">
         <v>46069</v>
@@ -6369,7 +6369,7 @@
         <v>18</v>
       </c>
       <c r="E247" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F247" s="2">
         <v>46069</v>
@@ -6386,7 +6386,7 @@
         <v>6</v>
       </c>
       <c r="E248" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F248" s="2">
         <v>46069</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0565D286-374F-4355-A9F9-6E1FB8E44D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB29BD7-CF83-49B5-91AB-66DB6ECCC50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1560" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -6403,7 +6403,7 @@
         <v>18</v>
       </c>
       <c r="E249" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F249" s="2">
         <v>46069</v>
@@ -6535,7 +6535,7 @@
         <v>18</v>
       </c>
       <c r="E258" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F258" s="2">
         <v>46069</v>
@@ -6569,7 +6569,7 @@
         <v>6</v>
       </c>
       <c r="E260" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F260" s="2">
         <v>46069</v>
@@ -6586,7 +6586,7 @@
         <v>4</v>
       </c>
       <c r="E261" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F261" s="2">
         <v>46070</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB29BD7-CF83-49B5-91AB-66DB6ECCC50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD84B5C-C546-4760-9887-6A6D4B3286C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -6603,7 +6603,7 @@
         <v>6</v>
       </c>
       <c r="E262" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F262" s="2">
         <v>46070</v>
@@ -6625,7 +6625,7 @@
         <v>4</v>
       </c>
       <c r="E264" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F264" s="2">
         <v>46070</v>
@@ -6642,7 +6642,7 @@
         <v>4</v>
       </c>
       <c r="E265" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F265" s="2">
         <v>46070</v>
@@ -6659,7 +6659,7 @@
         <v>4</v>
       </c>
       <c r="E266" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F266" s="2">
         <v>46070</v>
@@ -6676,7 +6676,7 @@
         <v>9</v>
       </c>
       <c r="E267" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F267" s="2">
         <v>46070</v>
@@ -6693,7 +6693,7 @@
         <v>4</v>
       </c>
       <c r="E268" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F268" s="2">
         <v>46070</v>
@@ -6715,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="E270" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F270" s="2">
         <v>46070</v>
@@ -6732,7 +6732,7 @@
         <v>7</v>
       </c>
       <c r="E271" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F271" s="2">
         <v>46070</v>
@@ -6749,7 +6749,7 @@
         <v>7</v>
       </c>
       <c r="E272" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F272" s="2">
         <v>46070</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD84B5C-C546-4760-9887-6A6D4B3286C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9710FE-6392-4E02-B21E-8BCB51DE984C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -6766,7 +6766,7 @@
         <v>7</v>
       </c>
       <c r="E273" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F273" s="2">
         <v>46070</v>
@@ -6783,7 +6783,7 @@
         <v>2</v>
       </c>
       <c r="E274" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
       <c r="F274" s="2">
         <v>46070</v>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9710FE-6392-4E02-B21E-8BCB51DE984C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8F9D27-36D8-4B27-A981-BB3E35928789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8F9D27-36D8-4B27-A981-BB3E35928789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB10B23-45B5-4C02-94DA-ACBECBCD1D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1170" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="679">
   <si>
     <t>Файл Архитектуры</t>
   </si>
@@ -2066,6 +2066,15 @@
   </si>
   <si>
     <t>Добавить Focal Loss как альтернативу CrossEntropy. Она фокусирует обучение на "сложных" примерах, где модель чаще ошибается. Focal Loss и Label Smoothing — альтернативные методы. Рекомендуется проводить ablation studies перед их одновременным использованием</t>
+  </si>
+  <si>
+    <t>При компиляции cargo build огромное количество места на диске нужно и не хватает даже 20 ГБ. Поэтому мы разработали план по оптимизации компиляции.</t>
+  </si>
+  <si>
+    <t>301-files-podkachki-optimization.md</t>
+  </si>
+  <si>
+    <t>Оптимизация памяти</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79095C0B-B83E-40CC-A743-D900B6CFAAA2}">
-  <dimension ref="A1:H342"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7609,7 +7618,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
         <v>646</v>
       </c>
@@ -7623,7 +7632,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>648</v>
       </c>
@@ -7637,7 +7646,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>650</v>
       </c>
@@ -7651,7 +7660,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
         <v>652</v>
       </c>
@@ -7665,7 +7674,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
         <v>654</v>
       </c>
@@ -7679,7 +7688,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
         <v>656</v>
       </c>
@@ -7691,6 +7700,23 @@
       </c>
       <c r="E342" t="s">
         <v>665</v>
+      </c>
+    </row>
+    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>677</v>
+      </c>
+      <c r="C343" t="s">
+        <v>676</v>
+      </c>
+      <c r="D343" t="s">
+        <v>678</v>
+      </c>
+      <c r="E343" t="s">
+        <v>674</v>
+      </c>
+      <c r="F343" s="2">
+        <v>46080</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB10B23-45B5-4C02-94DA-ACBECBCD1D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B61A5B-75CC-4EB6-8CB6-1D0D6864427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="780" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="685">
   <si>
     <t>Файл Архитектуры</t>
   </si>
@@ -2075,6 +2075,24 @@
   </si>
   <si>
     <t>Оптимизация памяти</t>
+  </si>
+  <si>
+    <t>302-dump-websocket-uproshenie-connect.md</t>
+  </si>
+  <si>
+    <t>Сейчас у нас бот подключался к Websocket слишком сложно. Я взял пример из старого бота и переписал подключение по его примеру боеле просто. Там одно подключение на все монеты и без доп. Защиты. Fix TLS Handshake</t>
+  </si>
+  <si>
+    <t>ЗАВЕРШЕНО</t>
+  </si>
+  <si>
+    <t>Выключаем этот блок. Не нужно вообще, определяет якобы волатильность рынка.</t>
+  </si>
+  <si>
+    <t>303-python-lab-train-memory-and-normalization-optimization.md</t>
+  </si>
+  <si>
+    <t>В задаче 127 мы создали нормализацию 3D векторную, она жрет очень много памяти. Теперь переделываем, упрощаяя ее.</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79095C0B-B83E-40CC-A743-D900B6CFAAA2}">
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -5267,7 +5285,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>370</v>
       </c>
@@ -5283,8 +5301,11 @@
       <c r="F177" s="2">
         <v>46066</v>
       </c>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G177" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>372</v>
       </c>
@@ -5301,7 +5322,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>374</v>
       </c>
@@ -5318,7 +5339,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>376</v>
       </c>
@@ -5335,7 +5356,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>378</v>
       </c>
@@ -5352,7 +5373,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>380</v>
       </c>
@@ -5369,12 +5390,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>671</v>
       </c>
@@ -5391,7 +5412,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>383</v>
       </c>
@@ -5408,7 +5429,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>385</v>
       </c>
@@ -5425,7 +5446,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
         <v>387</v>
       </c>
@@ -5442,7 +5463,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>389</v>
       </c>
@@ -5459,7 +5480,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>391</v>
       </c>
@@ -5476,7 +5497,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
         <v>393</v>
       </c>
@@ -5493,7 +5514,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
         <v>395</v>
       </c>
@@ -5510,7 +5531,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
         <v>397</v>
       </c>
@@ -7717,6 +7738,40 @@
       </c>
       <c r="F343" s="2">
         <v>46080</v>
+      </c>
+    </row>
+    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>679</v>
+      </c>
+      <c r="C344" t="s">
+        <v>680</v>
+      </c>
+      <c r="D344" t="s">
+        <v>1</v>
+      </c>
+      <c r="E344" t="s">
+        <v>681</v>
+      </c>
+      <c r="F344" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
+        <v>683</v>
+      </c>
+      <c r="C345" t="s">
+        <v>684</v>
+      </c>
+      <c r="D345" t="s">
+        <v>7</v>
+      </c>
+      <c r="E345" t="s">
+        <v>674</v>
+      </c>
+      <c r="F345" s="2">
+        <v>46084</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B61A5B-75CC-4EB6-8CB6-1D0D6864427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3737D2-2E5A-410B-B382-B875DAF0F6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1170" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3737D2-2E5A-410B-B382-B875DAF0F6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCFDD81-DD6D-470E-81F8-4075985EC62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="630" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="2205" yWindow="420" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="687">
   <si>
     <t>Файл Архитектуры</t>
   </si>
@@ -2093,6 +2093,12 @@
   </si>
   <si>
     <t>В задаче 127 мы создали нормализацию 3D векторную, она жрет очень много памяти. Теперь переделываем, упрощаяя ее.</t>
+  </si>
+  <si>
+    <t>304-python-data-error-gradient-explore-edit.md</t>
+  </si>
+  <si>
+    <t>Решаем проблему с взрывом градиентов (неправильной нарезке загруженных данны хи нормализации в Python обучение. Исправление ошибки разрыва градиента - неправильный порядок загрузки столбцов данных parquet - теперь загружаем по именам 202 столбца.</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79095C0B-B83E-40CC-A743-D900B6CFAAA2}">
-  <dimension ref="A1:H345"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7772,6 +7778,23 @@
       </c>
       <c r="F345" s="2">
         <v>46084</v>
+      </c>
+    </row>
+    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B346" t="s">
+        <v>685</v>
+      </c>
+      <c r="C346" t="s">
+        <v>686</v>
+      </c>
+      <c r="D346" t="s">
+        <v>7</v>
+      </c>
+      <c r="E346" t="s">
+        <v>681</v>
+      </c>
+      <c r="F346" s="2">
+        <v>46086</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCFDD81-DD6D-470E-81F8-4075985EC62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69DA8E7-66CC-4D09-AEE8-EAF5E26614F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="420" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
+    <workbookView xWindow="1170" yWindow="1080" windowWidth="17130" windowHeight="10440" xr2:uid="{9FB94960-611E-4E50-9CE7-FAD7E251227B}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="689">
   <si>
     <t>Файл Архитектуры</t>
   </si>
@@ -2099,6 +2099,12 @@
   </si>
   <si>
     <t>Решаем проблему с взрывом градиентов (неправильной нарезке загруженных данны хи нормализации в Python обучение. Исправление ошибки разрыва градиента - неправильный порядок загрузки столбцов данных parquet - теперь загружаем по именам 202 столбца.</t>
+  </si>
+  <si>
+    <t>Исправление ошибок Python обучения: Неправильная логика взвешивания режимов (Regime Weighting) в multi-horizon. Compute_curvature_penalty не использует regime_id для инференса. DistillationLoss не поддерживает label_smoothing в soft loss.Отсутствие инициализации bias для bottleneck слоёв</t>
+  </si>
+  <si>
+    <t>305-python-train-weigh-multihorizon-soft-los-errors.md</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79095C0B-B83E-40CC-A743-D900B6CFAAA2}">
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7791,10 +7797,27 @@
         <v>7</v>
       </c>
       <c r="E346" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="F346" s="2">
         <v>46086</v>
+      </c>
+    </row>
+    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
+        <v>688</v>
+      </c>
+      <c r="C347" t="s">
+        <v>687</v>
+      </c>
+      <c r="D347" t="s">
+        <v>7</v>
+      </c>
+      <c r="E347" t="s">
+        <v>674</v>
+      </c>
+      <c r="F347" s="2">
+        <v>46087</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -8421,7 +8421,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G347" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G348" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19800" windowHeight="7845"/>
+    <workbookView windowWidth="19800" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -2099,7 +2099,7 @@
     <t>306-python-train-robust-normlization-vmesto-zscore.md</t>
   </si>
   <si>
-    <t>Включение Robust нормализации для высоковолатилньых мемкоинов. Отключение Z-Score нормализации, она только для BTC, ETH kexit.</t>
+    <t>Включение Robust нормализации для высоковолатилньых мемкоинов. Отключение Z-Score нормализации, она только для BTC, ETH. Задача 306-2: "Data Integrity &amp; Column Safety". Задача 306-3: "Full Numerical Stability". Задача 306-4 "Total Column Sovereignty"</t>
   </si>
 </sst>
 </file>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19800" windowHeight="7125"/>
+    <workbookView windowWidth="19800" windowHeight="7845"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="693">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2063,6 +2063,9 @@
     <t xml:space="preserve">Проведение финального приемочного теста всей системы в реальных условиях. Официальный запуск фермы ботов в промышленную эксплуатацию. </t>
   </si>
   <si>
+    <t>ФАЗА-41 - Обучение Python - исправление ошибок</t>
+  </si>
+  <si>
     <t>301-files-podkachki-optimization.md</t>
   </si>
   <si>
@@ -2100,6 +2103,12 @@
   </si>
   <si>
     <t>Включение Robust нормализации для высоковолатилньых мемкоинов. Отключение Z-Score нормализации, она только для BTC, ETH. Задача 306-2: "Data Integrity &amp; Column Safety". Задача 306-3: "Full Numerical Stability". Задача 306-4 "Total Column Sovereignty"</t>
+  </si>
+  <si>
+    <t>307--</t>
+  </si>
+  <si>
+    <t>Стабилизация  Multi-Task.  Замена Clamp на SymLog. Ревизия и чистка балансировки. Адаптивное мечение. QK-Normalization</t>
   </si>
 </sst>
 </file>
@@ -3067,7 +3076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H348"/>
+  <dimension ref="A1:H350"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8318,63 +8327,51 @@
         <v>548</v>
       </c>
     </row>
-    <row r="343" spans="2:6">
+    <row r="343" spans="2:2">
       <c r="B343" t="s">
         <v>677</v>
       </c>
-      <c r="C343" t="s">
-        <v>678</v>
-      </c>
-      <c r="D343" t="s">
-        <v>679</v>
-      </c>
-      <c r="E343" t="s">
-        <v>19</v>
-      </c>
-      <c r="F343" s="2">
-        <v>46080</v>
-      </c>
     </row>
     <row r="344" spans="2:6">
       <c r="B344" t="s">
+        <v>678</v>
+      </c>
+      <c r="C344" t="s">
+        <v>679</v>
+      </c>
+      <c r="D344" t="s">
         <v>680</v>
       </c>
-      <c r="C344" t="s">
-        <v>681</v>
-      </c>
-      <c r="D344" t="s">
-        <v>13</v>
-      </c>
       <c r="E344" t="s">
         <v>19</v>
       </c>
       <c r="F344" s="2">
-        <v>46082</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="345" spans="2:6">
       <c r="B345" t="s">
+        <v>681</v>
+      </c>
+      <c r="C345" t="s">
         <v>682</v>
       </c>
-      <c r="C345" t="s">
-        <v>683</v>
-      </c>
       <c r="D345" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E345" t="s">
         <v>19</v>
       </c>
       <c r="F345" s="2">
-        <v>46084</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="346" spans="2:6">
       <c r="B346" t="s">
+        <v>683</v>
+      </c>
+      <c r="C346" t="s">
         <v>684</v>
-      </c>
-      <c r="C346" t="s">
-        <v>685</v>
       </c>
       <c r="D346" t="s">
         <v>20</v>
@@ -8383,15 +8380,15 @@
         <v>19</v>
       </c>
       <c r="F346" s="2">
-        <v>46086</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="347" spans="2:6">
       <c r="B347" t="s">
+        <v>685</v>
+      </c>
+      <c r="C347" t="s">
         <v>686</v>
-      </c>
-      <c r="C347" t="s">
-        <v>687</v>
       </c>
       <c r="D347" t="s">
         <v>20</v>
@@ -8400,15 +8397,15 @@
         <v>19</v>
       </c>
       <c r="F347" s="2">
-        <v>46087</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="348" spans="2:6">
       <c r="B348" t="s">
+        <v>687</v>
+      </c>
+      <c r="C348" t="s">
         <v>688</v>
-      </c>
-      <c r="C348" t="s">
-        <v>689</v>
       </c>
       <c r="D348" t="s">
         <v>20</v>
@@ -8417,7 +8414,32 @@
         <v>19</v>
       </c>
       <c r="F348" s="2">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="349" spans="2:6">
+      <c r="B349" t="s">
+        <v>689</v>
+      </c>
+      <c r="C349" t="s">
+        <v>690</v>
+      </c>
+      <c r="D349" t="s">
+        <v>20</v>
+      </c>
+      <c r="E349" t="s">
+        <v>19</v>
+      </c>
+      <c r="F349" s="2">
         <v>46088</v>
+      </c>
+    </row>
+    <row r="350" spans="2:3">
+      <c r="B350" t="s">
+        <v>691</v>
+      </c>
+      <c r="C350" t="s">
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$350</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="695">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2105,10 +2105,16 @@
     <t>Включение Robust нормализации для высоковолатилньых мемкоинов. Отключение Z-Score нормализации, она только для BTC, ETH. Задача 306-2: "Data Integrity &amp; Column Safety". Задача 306-3: "Full Numerical Stability". Задача 306-4 "Total Column Sovereignty"</t>
   </si>
   <si>
-    <t>307--</t>
+    <t>307-python-train-multitask-symlog-qknormal.md</t>
   </si>
   <si>
     <t>Стабилизация  Multi-Task.  Замена Clamp на SymLog. Ревизия и чистка балансировки. Адаптивное мечение. QK-Normalization</t>
+  </si>
+  <si>
+    <t>308-python-features-vib-past-returns-normalisation.md</t>
+  </si>
+  <si>
+    <t>Переделываем расчет VIP и Past Returns с нормализацией Robusta. Раньше эти два индикатора ошибочно загружались из сырых данных parquet. Код ожидал, что они там есть и не считал их на лету в Python. Теперь мы разобрались, что инчего в parquet кроме сырых ask, bid и времени нет. Там нет и не будет никаких индикаторов ,все считается в pythonyf ktne/</t>
   </si>
 </sst>
 </file>
@@ -3076,7 +3082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H350"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8434,16 +8440,42 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="350" spans="2:3">
+    <row r="350" spans="2:6">
       <c r="B350" t="s">
         <v>691</v>
       </c>
       <c r="C350" t="s">
         <v>692</v>
       </c>
+      <c r="D350" t="s">
+        <v>20</v>
+      </c>
+      <c r="E350" t="s">
+        <v>19</v>
+      </c>
+      <c r="F350" s="2">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="351" spans="2:6">
+      <c r="B351" t="s">
+        <v>693</v>
+      </c>
+      <c r="C351" t="s">
+        <v>694</v>
+      </c>
+      <c r="D351" t="s">
+        <v>20</v>
+      </c>
+      <c r="E351" t="s">
+        <v>19</v>
+      </c>
+      <c r="F351" s="2">
+        <v>46091</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G348" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G350" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$352</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="697">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2115,6 +2115,12 @@
   </si>
   <si>
     <t>Переделываем расчет VIP и Past Returns с нормализацией Robusta. Раньше эти два индикатора ошибочно загружались из сырых данных parquet. Код ожидал, что они там есть и не считал их на лету в Python. Теперь мы разобрались, что инчего в parquet кроме сырых ask, bid и времени нет. Там нет и не будет никаких индикаторов ,все считается в pythonyf ktne/</t>
+  </si>
+  <si>
+    <t>309-python-train-threshold-multiplier-static.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treshold решили установить статичный. В результате теста определили, лучший Threshold - лучший: 0.0004 (0.04%) для оризонта в 100 тиков. И сами его устанавливать при запуске обучения командой  --threshold_X.X. Важно ,что в будущем мы планируем сделать мультигоризонт и часть кода уже реализована. Чтобы мы предсказывали ондовременно на 50, 100, 200 тиков, и для каждого свой Threshold. Так мы определим оптимальный treshold конкретно для определенной монеты. </t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H352"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8474,8 +8480,25 @@
         <v>46091</v>
       </c>
     </row>
+    <row r="352" spans="2:6">
+      <c r="B352" t="s">
+        <v>695</v>
+      </c>
+      <c r="C352" t="s">
+        <v>696</v>
+      </c>
+      <c r="D352" t="s">
+        <v>20</v>
+      </c>
+      <c r="E352" t="s">
+        <v>19</v>
+      </c>
+      <c r="F352" s="2">
+        <v>46091</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G350" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G352" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="699">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2121,6 +2121,12 @@
   </si>
   <si>
     <t xml:space="preserve">Treshold решили установить статичный. В результате теста определили, лучший Threshold - лучший: 0.0004 (0.04%) для оризонта в 100 тиков. И сами его устанавливать при запуске обучения командой  --threshold_X.X. Важно ,что в будущем мы планируем сделать мультигоризонт и часть кода уже реализована. Чтобы мы предсказывали ондовременно на 50, 100, 200 тиков, и для каждого свой Threshold. Так мы определим оптимальный treshold конкретно для определенной монеты. </t>
+  </si>
+  <si>
+    <t>310-python-train-errors-symlog-pastreturn-attention-pooling.md</t>
+  </si>
+  <si>
+    <t>Исправляем ошибки обучения Python - Двойной SymLog, PastReturns, Attention Pooling в LOBPatching</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H352"/>
+  <dimension ref="A1:H353"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8497,6 +8503,20 @@
         <v>46091</v>
       </c>
     </row>
+    <row r="353" spans="2:6">
+      <c r="B353" t="s">
+        <v>697</v>
+      </c>
+      <c r="C353" t="s">
+        <v>698</v>
+      </c>
+      <c r="D353" t="s">
+        <v>20</v>
+      </c>
+      <c r="F353" s="2">
+        <v>46092</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G352" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="702">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2075,6 +2075,9 @@
     <t>Оптимизация памяти</t>
   </si>
   <si>
+    <t>ЗАВЕРШЕНО</t>
+  </si>
+  <si>
     <t>302-dump-websocket-uproshenie-connect.md</t>
   </si>
   <si>
@@ -2127,6 +2130,12 @@
   </si>
   <si>
     <t>Исправляем ошибки обучения Python - Двойной SymLog, PastReturns, Attention Pooling в LOBPatching</t>
+  </si>
+  <si>
+    <t>311-python-normalization-chanels-export-onnx-massiv.md</t>
+  </si>
+  <si>
+    <t>Исправление несоответствия Python-Rust в формировании каналов. Исправление Неправильный формат экспорта ONNX. Исправление ошибки: Логи печатаются ДО нормализации.  Изменить метод _init_memory_mode. Изменить метод  _process_sample.</t>
   </si>
 </sst>
 </file>
@@ -3094,7 +3103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H353"/>
+  <dimension ref="A1:H354"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8361,7 +8370,7 @@
         <v>680</v>
       </c>
       <c r="E344" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F344" s="2">
         <v>46080</v>
@@ -8369,16 +8378,16 @@
     </row>
     <row r="345" spans="2:6">
       <c r="B345" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C345" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D345" t="s">
         <v>13</v>
       </c>
       <c r="E345" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F345" s="2">
         <v>46082</v>
@@ -8386,16 +8395,16 @@
     </row>
     <row r="346" spans="2:6">
       <c r="B346" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C346" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D346" t="s">
         <v>20</v>
       </c>
       <c r="E346" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F346" s="2">
         <v>46084</v>
@@ -8403,16 +8412,16 @@
     </row>
     <row r="347" spans="2:6">
       <c r="B347" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C347" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D347" t="s">
         <v>20</v>
       </c>
       <c r="E347" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F347" s="2">
         <v>46086</v>
@@ -8420,16 +8429,16 @@
     </row>
     <row r="348" spans="2:6">
       <c r="B348" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C348" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D348" t="s">
         <v>20</v>
       </c>
       <c r="E348" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F348" s="2">
         <v>46087</v>
@@ -8437,16 +8446,16 @@
     </row>
     <row r="349" spans="2:6">
       <c r="B349" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C349" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D349" t="s">
         <v>20</v>
       </c>
       <c r="E349" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F349" s="2">
         <v>46088</v>
@@ -8454,16 +8463,16 @@
     </row>
     <row r="350" spans="2:6">
       <c r="B350" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C350" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D350" t="s">
         <v>20</v>
       </c>
       <c r="E350" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F350" s="2">
         <v>46091</v>
@@ -8471,16 +8480,16 @@
     </row>
     <row r="351" spans="2:6">
       <c r="B351" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C351" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D351" t="s">
         <v>20</v>
       </c>
       <c r="E351" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F351" s="2">
         <v>46091</v>
@@ -8488,16 +8497,16 @@
     </row>
     <row r="352" spans="2:6">
       <c r="B352" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C352" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D352" t="s">
         <v>20</v>
       </c>
       <c r="E352" t="s">
-        <v>19</v>
+        <v>681</v>
       </c>
       <c r="F352" s="2">
         <v>46091</v>
@@ -8505,15 +8514,32 @@
     </row>
     <row r="353" spans="2:6">
       <c r="B353" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C353" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D353" t="s">
         <v>20</v>
       </c>
+      <c r="E353" t="s">
+        <v>681</v>
+      </c>
       <c r="F353" s="2">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="354" spans="2:6">
+      <c r="B354" t="s">
+        <v>700</v>
+      </c>
+      <c r="C354" t="s">
+        <v>701</v>
+      </c>
+      <c r="D354" t="s">
+        <v>20</v>
+      </c>
+      <c r="F354" s="2">
         <v>46092</v>
       </c>
     </row>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$354</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="702">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2135,7 +2135,7 @@
     <t>311-python-normalization-chanels-export-onnx-massiv.md</t>
   </si>
   <si>
-    <t>Исправление несоответствия Python-Rust в формировании каналов. Исправление Неправильный формат экспорта ONNX. Исправление ошибки: Логи печатаются ДО нормализации.  Изменить метод _init_memory_mode. Изменить метод  _process_sample.</t>
+    <t>Исправление несоответствия Python-Rust в формировании каналов. Исправление Неправильный формат экспорта ONNX. Исправление ошибки: Логи печатаются ДО нормализации.  Изменить метод _init_memory_mode. Изменить метод  _process_sample. Так же отключили (заккоментирвоали методы streaming, memap, чтоб хотябы 1 режим memory нормально настроить)</t>
   </si>
 </sst>
 </file>
@@ -8539,12 +8539,15 @@
       <c r="D354" t="s">
         <v>20</v>
       </c>
+      <c r="E354" t="s">
+        <v>681</v>
+      </c>
       <c r="F354" s="2">
         <v>46092</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G352" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G354" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="704">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2136,6 +2136,12 @@
   </si>
   <si>
     <t>Исправление несоответствия Python-Rust в формировании каналов. Исправление Неправильный формат экспорта ONNX. Исправление ошибки: Логи печатаются ДО нормализации.  Изменить метод _init_memory_mode. Изменить метод  _process_sample. Так же отключили (заккоментирвоали методы streaming, memap, чтоб хотябы 1 режим memory нормально настроить)</t>
+  </si>
+  <si>
+    <t>312-python-train-faster-curvature-tensorboard-batch-size.md</t>
+  </si>
+  <si>
+    <t>Проблема- каждая эпоха долго идет по 25 мин. Оптимизация: Отключить Curvature Regularization. Оптимизировать частоту TensorBoard. Добавить PyTorch Profiler. Оптимизировать DataLoader. Batch Size 64.</t>
   </si>
 </sst>
 </file>
@@ -3103,7 +3109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H354"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8546,6 +8552,23 @@
         <v>46092</v>
       </c>
     </row>
+    <row r="355" spans="2:6">
+      <c r="B355" t="s">
+        <v>702</v>
+      </c>
+      <c r="C355" t="s">
+        <v>703</v>
+      </c>
+      <c r="D355" t="s">
+        <v>20</v>
+      </c>
+      <c r="E355" t="s">
+        <v>681</v>
+      </c>
+      <c r="F355" s="2">
+        <v>46093</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G354" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19800" windowHeight="7845"/>
+    <workbookView windowWidth="20400" windowHeight="7845"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$354</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$355</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="706">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2142,6 +2142,12 @@
   </si>
   <si>
     <t>Проблема- каждая эпоха долго идет по 25 мин. Оптимизация: Отключить Curvature Regularization. Оптимизировать частоту TensorBoard. Добавить PyTorch Profiler. Оптимизировать DataLoader. Batch Size 64.</t>
+  </si>
+  <si>
+    <t>313-python-train-adaprive-lr-loss-weight.md</t>
+  </si>
+  <si>
+    <t>Adaptive LR (Loss-based) внедряем в обучение Python. Если Loss падает стабильно — мы можем чуть ускорить шаг. Если Loss начинает колебаться или расти — замедляемся. Должно увеличить MCC и внимание на редких классах</t>
   </si>
 </sst>
 </file>
@@ -3109,7 +3115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H356"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
@@ -8569,8 +8575,22 @@
         <v>46093</v>
       </c>
     </row>
+    <row r="356" spans="2:6">
+      <c r="B356" t="s">
+        <v>704</v>
+      </c>
+      <c r="C356" t="s">
+        <v>705</v>
+      </c>
+      <c r="D356" t="s">
+        <v>20</v>
+      </c>
+      <c r="F356" s="2">
+        <v>46094</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G354" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G355" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -10,7 +10,7 @@
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">АРХИТЕКТУРА!$A$1:$G$356</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="706">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2147,7 +2147,7 @@
     <t>313-python-train-adaprive-lr-loss-weight.md</t>
   </si>
   <si>
-    <t>Adaptive LR (Loss-based) внедряем в обучение Python. Если Loss падает стабильно — мы можем чуть ускорить шаг. Если Loss начинает колебаться или расти — замедляемся. Должно увеличить MCC и внимание на редких классах</t>
+    <t>Adaptive LR (Loss-based) внедряем в обучение Python. Если Loss падает стабильно — мы можем чуть ускорить шаг. Если Loss начинает колебаться или расти — замедляемся. Должно увеличить MCC и внимание на редких классах. Так же добавил расширенную аналитику для эпох: Theoretical Edge, Signal Confidence Analysis, Directional Accuracy, LOB Imbalance Alignment</t>
   </si>
 </sst>
 </file>
@@ -8585,12 +8585,15 @@
       <c r="D356" t="s">
         <v>20</v>
       </c>
+      <c r="E356" t="s">
+        <v>681</v>
+      </c>
       <c r="F356" s="2">
         <v>46094</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G355" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G356" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5E6643-0B99-4535-952E-3E412E9ED7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20400" windowHeight="7845"/>
+    <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="710">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2148,20 +2154,28 @@
   </si>
   <si>
     <t>Adaptive LR (Loss-based) внедряем в обучение Python. Если Loss падает стабильно — мы можем чуть ускорить шаг. Если Loss начинает колебаться или расти — замедляемся. Должно увеличить MCC и внимание на редких классах. Так же добавил расширенную аналитику для эпох: Theoretical Edge, Signal Confidence Analysis, Directional Accuracy, LOB Imbalance Alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исправление ошибок OFI нормализации и корректировка весов классов. OFI индикатор не правильно нормализован, нормализуетсяна каждом уровне и имбаланс накапливается. Мы же должны его нормализовать в финале. </t>
+  </si>
+  <si>
+    <t>314-python-train-ofi-imblanace-normalize.md</t>
+  </si>
+  <si>
+    <t>315-python-train-func-chanels-normalization-vol-ofi.md</t>
+  </si>
+  <si>
+    <t>Исправить функции расчета каналов и их нормализации в dataset.py VOL, OFI. До этого все to была двойная нормализация и неправилньые формы логарифмирования Объемов, котоыре каждый урвоень считали отдельно и суммировали.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="dd\.mmm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2184,159 +2198,8 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2345,198 +2208,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2544,314 +2221,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3109,23 +2500,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H356"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H358"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
-    <col min="2" max="2" width="33.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="52.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="8.42857142857143" customWidth="1"/>
-    <col min="5" max="5" width="11.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3148,7 +2539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3168,7 +2559,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3176,7 +2567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3196,7 +2587,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3216,7 +2607,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -3236,7 +2627,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3256,7 +2647,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -3276,7 +2667,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -3296,7 +2687,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3316,7 +2707,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -3336,7 +2727,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -3356,7 +2747,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -3364,7 +2755,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -3384,7 +2775,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -3401,7 +2792,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>48</v>
       </c>
@@ -3418,7 +2809,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>50</v>
       </c>
@@ -3435,7 +2826,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>52</v>
       </c>
@@ -3452,7 +2843,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>54</v>
       </c>
@@ -3469,7 +2860,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>56</v>
       </c>
@@ -3486,7 +2877,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>58</v>
       </c>
@@ -3503,7 +2894,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>60</v>
       </c>
@@ -3520,7 +2911,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>62</v>
       </c>
@@ -3537,7 +2928,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>64</v>
       </c>
@@ -3554,12 +2945,12 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>67</v>
       </c>
@@ -3576,7 +2967,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>69</v>
       </c>
@@ -3593,7 +2984,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>71</v>
       </c>
@@ -3610,7 +3001,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>73</v>
       </c>
@@ -3627,7 +3018,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>75</v>
       </c>
@@ -3644,7 +3035,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>77</v>
       </c>
@@ -3661,7 +3052,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>79</v>
       </c>
@@ -3678,7 +3069,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>81</v>
       </c>
@@ -3695,7 +3086,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>83</v>
       </c>
@@ -3712,7 +3103,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>85</v>
       </c>
@@ -3729,7 +3120,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>87</v>
       </c>
@@ -3746,7 +3137,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>89</v>
       </c>
@@ -3763,12 +3154,12 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>92</v>
       </c>
@@ -3785,7 +3176,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>94</v>
       </c>
@@ -3802,7 +3193,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>96</v>
       </c>
@@ -3819,7 +3210,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>98</v>
       </c>
@@ -3836,7 +3227,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>100</v>
       </c>
@@ -3853,7 +3244,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>102</v>
       </c>
@@ -3870,12 +3261,12 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>105</v>
       </c>
@@ -3892,7 +3283,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>107</v>
       </c>
@@ -3909,7 +3300,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>109</v>
       </c>
@@ -3926,7 +3317,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>111</v>
       </c>
@@ -3943,7 +3334,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>113</v>
       </c>
@@ -3960,7 +3351,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>115</v>
       </c>
@@ -3977,7 +3368,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>117</v>
       </c>
@@ -3994,7 +3385,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>119</v>
       </c>
@@ -4011,7 +3402,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>121</v>
       </c>
@@ -4028,7 +3419,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>123</v>
       </c>
@@ -4045,7 +3436,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>125</v>
       </c>
@@ -4062,7 +3453,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>127</v>
       </c>
@@ -4079,12 +3470,12 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="58" spans="2:2">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>130</v>
       </c>
@@ -4101,7 +3492,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>132</v>
       </c>
@@ -4118,7 +3509,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>134</v>
       </c>
@@ -4135,7 +3526,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>136</v>
       </c>
@@ -4152,7 +3543,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>138</v>
       </c>
@@ -4169,7 +3560,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>140</v>
       </c>
@@ -4186,7 +3577,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>142</v>
       </c>
@@ -4203,7 +3594,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>144</v>
       </c>
@@ -4220,7 +3611,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="67" spans="2:6">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>146</v>
       </c>
@@ -4237,7 +3628,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="68" spans="2:6">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>148</v>
       </c>
@@ -4254,12 +3645,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="69" spans="2:2">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>151</v>
       </c>
@@ -4276,7 +3667,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>153</v>
       </c>
@@ -4293,7 +3684,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>155</v>
       </c>
@@ -4310,7 +3701,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="73" spans="2:6">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>157</v>
       </c>
@@ -4327,7 +3718,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>159</v>
       </c>
@@ -4344,7 +3735,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>161</v>
       </c>
@@ -4361,7 +3752,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>164</v>
       </c>
@@ -4378,7 +3769,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>166</v>
       </c>
@@ -4395,7 +3786,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="78" spans="2:6">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>168</v>
       </c>
@@ -4412,7 +3803,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="79" spans="2:6">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>170</v>
       </c>
@@ -4429,12 +3820,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="80" spans="2:2">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="81" spans="2:6">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>173</v>
       </c>
@@ -4451,7 +3842,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="82" spans="2:6">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>175</v>
       </c>
@@ -4468,7 +3859,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="83" spans="2:6">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>177</v>
       </c>
@@ -4485,7 +3876,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>179</v>
       </c>
@@ -4502,7 +3893,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="85" spans="2:6">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>181</v>
       </c>
@@ -4519,12 +3910,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="86" spans="2:2">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>184</v>
       </c>
@@ -4541,7 +3932,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>186</v>
       </c>
@@ -4558,7 +3949,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>188</v>
       </c>
@@ -4575,7 +3966,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>190</v>
       </c>
@@ -4592,7 +3983,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="91" spans="2:6">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>192</v>
       </c>
@@ -4609,12 +4000,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="92" spans="2:2">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>195</v>
       </c>
@@ -4631,7 +4022,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="94" spans="2:6">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>198</v>
       </c>
@@ -4648,7 +4039,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="95" spans="2:6">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>200</v>
       </c>
@@ -4665,7 +4056,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="96" spans="2:6">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>202</v>
       </c>
@@ -4682,7 +4073,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="97" spans="2:7">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>204</v>
       </c>
@@ -4702,12 +4093,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="98" spans="2:2">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="99" spans="2:6">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>208</v>
       </c>
@@ -4724,7 +4115,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>210</v>
       </c>
@@ -4741,7 +4132,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>212</v>
       </c>
@@ -4758,7 +4149,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>214</v>
       </c>
@@ -4775,7 +4166,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>216</v>
       </c>
@@ -4792,12 +4183,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="104" spans="2:2">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>219</v>
       </c>
@@ -4814,7 +4205,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>221</v>
       </c>
@@ -4831,7 +4222,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>223</v>
       </c>
@@ -4848,7 +4239,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>225</v>
       </c>
@@ -4865,7 +4256,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>227</v>
       </c>
@@ -4882,12 +4273,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="110" spans="2:2">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>230</v>
       </c>
@@ -4904,7 +4295,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>232</v>
       </c>
@@ -4921,7 +4312,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="113" spans="2:6">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>234</v>
       </c>
@@ -4938,7 +4329,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="114" spans="2:6">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>236</v>
       </c>
@@ -4955,7 +4346,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="115" spans="2:6">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>238</v>
       </c>
@@ -4972,12 +4363,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="116" spans="2:2">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="117" spans="2:6">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>241</v>
       </c>
@@ -4994,7 +4385,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>243</v>
       </c>
@@ -5011,7 +4402,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>245</v>
       </c>
@@ -5028,7 +4419,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>247</v>
       </c>
@@ -5045,7 +4436,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>249</v>
       </c>
@@ -5062,7 +4453,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>251</v>
       </c>
@@ -5079,7 +4470,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="123" spans="2:6">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>253</v>
       </c>
@@ -5096,7 +4487,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="124" spans="2:6">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>255</v>
       </c>
@@ -5113,7 +4504,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="125" spans="2:6">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>257</v>
       </c>
@@ -5130,7 +4521,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="126" spans="2:6">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>259</v>
       </c>
@@ -5147,12 +4538,12 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="127" spans="2:2">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="128" spans="2:6">
+    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>262</v>
       </c>
@@ -5169,7 +4560,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="129" spans="2:6">
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>264</v>
       </c>
@@ -5186,7 +4577,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="130" spans="2:6">
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>266</v>
       </c>
@@ -5203,7 +4594,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>268</v>
       </c>
@@ -5220,7 +4611,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>270</v>
       </c>
@@ -5237,7 +4628,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>272</v>
       </c>
@@ -5254,7 +4645,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="134" spans="2:6">
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>274</v>
       </c>
@@ -5271,7 +4662,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>276</v>
       </c>
@@ -5288,7 +4679,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="136" spans="2:6">
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>278</v>
       </c>
@@ -5305,7 +4696,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>280</v>
       </c>
@@ -5322,12 +4713,12 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="138" spans="2:2">
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>283</v>
       </c>
@@ -5344,7 +4735,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="140" spans="2:6">
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>285</v>
       </c>
@@ -5361,7 +4752,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="141" spans="2:6">
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>287</v>
       </c>
@@ -5378,7 +4769,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="142" spans="2:6">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>289</v>
       </c>
@@ -5395,7 +4786,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>291</v>
       </c>
@@ -5412,7 +4803,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="144" spans="2:6">
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>293</v>
       </c>
@@ -5429,7 +4820,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="145" spans="2:6">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>295</v>
       </c>
@@ -5446,7 +4837,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="146" spans="2:6">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>297</v>
       </c>
@@ -5463,7 +4854,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>299</v>
       </c>
@@ -5480,7 +4871,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="148" spans="2:6">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>301</v>
       </c>
@@ -5497,12 +4888,12 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>304</v>
       </c>
@@ -5519,7 +4910,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="151" spans="2:6">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>306</v>
       </c>
@@ -5536,7 +4927,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>308</v>
       </c>
@@ -5553,7 +4944,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="153" spans="2:6">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>310</v>
       </c>
@@ -5570,7 +4961,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="154" spans="2:6">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
         <v>312</v>
       </c>
@@ -5587,7 +4978,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="155" spans="2:6">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>314</v>
       </c>
@@ -5604,7 +4995,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="156" spans="2:6">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>316</v>
       </c>
@@ -5621,7 +5012,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="157" spans="2:8">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>318</v>
       </c>
@@ -5641,7 +5032,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="158" spans="2:6">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>321</v>
       </c>
@@ -5658,7 +5049,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="159" spans="2:6">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>323</v>
       </c>
@@ -5675,12 +5066,12 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>326</v>
       </c>
@@ -5697,7 +5088,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="162" spans="2:6">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
         <v>328</v>
       </c>
@@ -5714,7 +5105,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="163" spans="2:6">
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>330</v>
       </c>
@@ -5731,7 +5122,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
         <v>332</v>
       </c>
@@ -5748,7 +5139,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
         <v>334</v>
       </c>
@@ -5765,12 +5156,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>337</v>
       </c>
@@ -5787,7 +5178,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>339</v>
       </c>
@@ -5804,7 +5195,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>341</v>
       </c>
@@ -5821,7 +5212,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="170" spans="2:6">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
         <v>343</v>
       </c>
@@ -5838,7 +5229,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="171" spans="2:6">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
         <v>345</v>
       </c>
@@ -5855,12 +5246,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="2:6">
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
         <v>348</v>
       </c>
@@ -5877,7 +5268,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="174" spans="2:6">
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>350</v>
       </c>
@@ -5894,7 +5285,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="175" spans="2:6">
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
         <v>352</v>
       </c>
@@ -5911,7 +5302,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="176" spans="2:6">
+    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>354</v>
       </c>
@@ -5928,7 +5319,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="177" spans="2:7">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>356</v>
       </c>
@@ -5948,7 +5339,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="178" spans="2:6">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>359</v>
       </c>
@@ -5965,7 +5356,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="179" spans="2:6">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>361</v>
       </c>
@@ -5982,7 +5373,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="180" spans="2:6">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>363</v>
       </c>
@@ -5999,7 +5390,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="181" spans="2:6">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>365</v>
       </c>
@@ -6016,7 +5407,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="182" spans="2:6">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>367</v>
       </c>
@@ -6033,12 +5424,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="184" spans="2:6">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>370</v>
       </c>
@@ -6055,7 +5446,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="185" spans="2:6">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>372</v>
       </c>
@@ -6072,7 +5463,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="186" spans="2:6">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>374</v>
       </c>
@@ -6089,7 +5480,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="187" spans="2:6">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
         <v>376</v>
       </c>
@@ -6106,7 +5497,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="188" spans="2:6">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>378</v>
       </c>
@@ -6123,7 +5514,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="189" spans="2:6">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>380</v>
       </c>
@@ -6140,7 +5531,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="190" spans="2:6">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
         <v>382</v>
       </c>
@@ -6157,7 +5548,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="191" spans="2:6">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
         <v>384</v>
       </c>
@@ -6174,7 +5565,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="192" spans="2:6">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
         <v>386</v>
       </c>
@@ -6191,7 +5582,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="193" spans="2:7">
+    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
         <v>388</v>
       </c>
@@ -6211,12 +5602,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="195" spans="2:6">
+    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
         <v>392</v>
       </c>
@@ -6233,7 +5624,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="196" spans="2:6">
+    <row r="196" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
         <v>394</v>
       </c>
@@ -6250,7 +5641,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="197" spans="2:6">
+    <row r="197" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
         <v>396</v>
       </c>
@@ -6267,7 +5658,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="198" spans="2:6">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
         <v>398</v>
       </c>
@@ -6284,7 +5675,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="199" spans="2:6">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
         <v>400</v>
       </c>
@@ -6301,7 +5692,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="200" spans="2:6">
+    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>402</v>
       </c>
@@ -6318,7 +5709,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="201" spans="2:6">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
         <v>404</v>
       </c>
@@ -6335,7 +5726,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="202" spans="2:6">
+    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>406</v>
       </c>
@@ -6352,7 +5743,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="203" spans="2:6">
+    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
         <v>408</v>
       </c>
@@ -6369,7 +5760,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="204" spans="2:6">
+    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
         <v>410</v>
       </c>
@@ -6386,12 +5777,12 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="206" spans="2:6">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>413</v>
       </c>
@@ -6408,7 +5799,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="207" spans="2:6">
+    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>415</v>
       </c>
@@ -6425,7 +5816,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="208" spans="2:6">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
         <v>417</v>
       </c>
@@ -6442,7 +5833,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="209" spans="2:6">
+    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
         <v>419</v>
       </c>
@@ -6459,7 +5850,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="210" spans="2:6">
+    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
         <v>421</v>
       </c>
@@ -6476,7 +5867,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="211" spans="2:6">
+    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
         <v>423</v>
       </c>
@@ -6493,7 +5884,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="212" spans="2:6">
+    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
         <v>425</v>
       </c>
@@ -6510,7 +5901,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="213" spans="2:6">
+    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
         <v>427</v>
       </c>
@@ -6527,7 +5918,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="214" spans="2:6">
+    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>429</v>
       </c>
@@ -6544,7 +5935,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="215" spans="2:6">
+    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
         <v>431</v>
       </c>
@@ -6561,12 +5952,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="217" spans="2:6">
+    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
         <v>434</v>
       </c>
@@ -6583,7 +5974,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="218" spans="2:6">
+    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
         <v>436</v>
       </c>
@@ -6600,7 +5991,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="219" spans="2:6">
+    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
         <v>438</v>
       </c>
@@ -6617,7 +6008,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="220" spans="2:6">
+    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>440</v>
       </c>
@@ -6634,7 +6025,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="221" spans="2:6">
+    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>442</v>
       </c>
@@ -6651,7 +6042,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="222" spans="2:6">
+    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>444</v>
       </c>
@@ -6668,7 +6059,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="223" spans="2:6">
+    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
         <v>446</v>
       </c>
@@ -6685,7 +6076,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="224" spans="2:6">
+    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
         <v>448</v>
       </c>
@@ -6702,7 +6093,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="225" spans="2:6">
+    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>450</v>
       </c>
@@ -6719,7 +6110,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="226" spans="2:6">
+    <row r="226" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
         <v>452</v>
       </c>
@@ -6736,12 +6127,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="227" spans="2:2">
+    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="2:6">
+    <row r="228" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
         <v>455</v>
       </c>
@@ -6758,7 +6149,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="229" spans="2:6">
+    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
         <v>457</v>
       </c>
@@ -6775,7 +6166,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="230" spans="2:6">
+    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
         <v>459</v>
       </c>
@@ -6792,7 +6183,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="231" spans="2:6">
+    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>461</v>
       </c>
@@ -6809,7 +6200,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="232" spans="2:6">
+    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
         <v>463</v>
       </c>
@@ -6826,12 +6217,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="233" spans="2:2">
+    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="2:6">
+    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
         <v>466</v>
       </c>
@@ -6848,7 +6239,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="235" spans="2:6">
+    <row r="235" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
         <v>468</v>
       </c>
@@ -6865,7 +6256,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="236" spans="2:6">
+    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
         <v>470</v>
       </c>
@@ -6882,7 +6273,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="237" spans="2:6">
+    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>472</v>
       </c>
@@ -6899,7 +6290,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="238" spans="2:7">
+    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B238" s="4" t="s">
         <v>474</v>
       </c>
@@ -6919,12 +6310,12 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="2:2">
+    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="2:6">
+    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>478</v>
       </c>
@@ -6941,7 +6332,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="241" spans="2:6">
+    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>480</v>
       </c>
@@ -6958,7 +6349,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="242" spans="2:6">
+    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>482</v>
       </c>
@@ -6975,7 +6366,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="243" spans="2:6">
+    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
         <v>484</v>
       </c>
@@ -6992,7 +6383,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="244" spans="2:6">
+    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
         <v>486</v>
       </c>
@@ -7009,12 +6400,12 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="245" spans="2:2">
+    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="246" spans="2:6">
+    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>489</v>
       </c>
@@ -7031,7 +6422,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="247" spans="2:6">
+    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>491</v>
       </c>
@@ -7048,7 +6439,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="248" spans="2:6">
+    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
         <v>493</v>
       </c>
@@ -7065,7 +6456,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="249" spans="2:6">
+    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
         <v>495</v>
       </c>
@@ -7082,7 +6473,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="250" spans="2:7">
+    <row r="250" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B250" s="4" t="s">
         <v>497</v>
       </c>
@@ -7102,12 +6493,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="2:2">
+    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="2:6">
+    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
         <v>502</v>
       </c>
@@ -7124,7 +6515,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="253" spans="2:6">
+    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
         <v>504</v>
       </c>
@@ -7141,7 +6532,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="254" spans="2:6">
+    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
         <v>506</v>
       </c>
@@ -7158,7 +6549,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="255" spans="2:6">
+    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
         <v>508</v>
       </c>
@@ -7175,7 +6566,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="256" spans="2:6">
+    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
         <v>510</v>
       </c>
@@ -7192,12 +6583,12 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="257" spans="2:2">
+    <row r="257" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="258" spans="2:6">
+    <row r="258" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
         <v>513</v>
       </c>
@@ -7214,7 +6605,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="259" spans="2:7">
+    <row r="259" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B259" s="4" t="s">
         <v>515</v>
       </c>
@@ -7231,7 +6622,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="260" spans="2:6">
+    <row r="260" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
         <v>519</v>
       </c>
@@ -7248,7 +6639,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="261" spans="2:6">
+    <row r="261" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
         <v>521</v>
       </c>
@@ -7265,7 +6656,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="262" spans="2:6">
+    <row r="262" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
         <v>523</v>
       </c>
@@ -7282,12 +6673,12 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="263" spans="2:2">
+    <row r="263" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="2:6">
+    <row r="264" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
         <v>526</v>
       </c>
@@ -7304,7 +6695,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="265" spans="2:6">
+    <row r="265" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
         <v>528</v>
       </c>
@@ -7321,7 +6712,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="266" spans="2:6">
+    <row r="266" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
         <v>530</v>
       </c>
@@ -7338,7 +6729,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="267" spans="2:6">
+    <row r="267" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
         <v>532</v>
       </c>
@@ -7355,7 +6746,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="268" spans="2:6">
+    <row r="268" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
         <v>534</v>
       </c>
@@ -7372,12 +6763,12 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="269" spans="2:2">
+    <row r="269" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="270" spans="2:6">
+    <row r="270" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
         <v>537</v>
       </c>
@@ -7394,7 +6785,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="271" spans="2:6">
+    <row r="271" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
         <v>539</v>
       </c>
@@ -7411,7 +6802,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="272" spans="2:6">
+    <row r="272" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
         <v>541</v>
       </c>
@@ -7428,7 +6819,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="273" spans="2:6">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
         <v>543</v>
       </c>
@@ -7445,7 +6836,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="274" spans="2:6">
+    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
         <v>545</v>
       </c>
@@ -7462,7 +6853,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="275" spans="2:5">
+    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
         <v>547</v>
       </c>
@@ -7470,7 +6861,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="2:5">
+    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
         <v>549</v>
       </c>
@@ -7484,7 +6875,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="277" spans="2:5">
+    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
         <v>551</v>
       </c>
@@ -7498,7 +6889,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="278" spans="2:5">
+    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
         <v>553</v>
       </c>
@@ -7512,7 +6903,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="279" spans="2:5">
+    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
         <v>555</v>
       </c>
@@ -7526,7 +6917,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="280" spans="2:5">
+    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
         <v>557</v>
       </c>
@@ -7540,7 +6931,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="2:5">
+    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
         <v>559</v>
       </c>
@@ -7548,7 +6939,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="282" spans="2:5">
+    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
         <v>560</v>
       </c>
@@ -7562,7 +6953,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="283" spans="2:5">
+    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
         <v>562</v>
       </c>
@@ -7576,7 +6967,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="284" spans="2:5">
+    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
         <v>564</v>
       </c>
@@ -7590,7 +6981,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="285" spans="2:5">
+    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
         <v>566</v>
       </c>
@@ -7604,7 +6995,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="286" spans="2:5">
+    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
         <v>568</v>
       </c>
@@ -7618,7 +7009,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="287" spans="2:5">
+    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
         <v>570</v>
       </c>
@@ -7626,7 +7017,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="288" spans="2:5">
+    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
         <v>571</v>
       </c>
@@ -7640,7 +7031,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="289" spans="2:5">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
         <v>574</v>
       </c>
@@ -7654,7 +7045,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="290" spans="2:5">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
         <v>576</v>
       </c>
@@ -7668,7 +7059,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="291" spans="2:5">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
         <v>578</v>
       </c>
@@ -7682,7 +7073,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="292" spans="2:5">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
         <v>580</v>
       </c>
@@ -7696,7 +7087,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="293" spans="2:5">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
         <v>582</v>
       </c>
@@ -7704,7 +7095,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="294" spans="2:5">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
         <v>583</v>
       </c>
@@ -7718,7 +7109,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="295" spans="2:5">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
         <v>585</v>
       </c>
@@ -7732,7 +7123,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="296" spans="2:5">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
         <v>587</v>
       </c>
@@ -7746,7 +7137,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="297" spans="2:5">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
         <v>589</v>
       </c>
@@ -7760,7 +7151,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="298" spans="2:5">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
         <v>591</v>
       </c>
@@ -7774,7 +7165,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="299" spans="2:5">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
         <v>593</v>
       </c>
@@ -7782,7 +7173,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="300" spans="2:5">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
         <v>594</v>
       </c>
@@ -7796,7 +7187,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="301" spans="2:5">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
         <v>596</v>
       </c>
@@ -7810,7 +7201,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="302" spans="2:5">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
         <v>598</v>
       </c>
@@ -7824,7 +7215,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="303" spans="2:5">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
         <v>600</v>
       </c>
@@ -7838,7 +7229,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="2:5">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
         <v>602</v>
       </c>
@@ -7852,7 +7243,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="2:5">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
         <v>604</v>
       </c>
@@ -7860,7 +7251,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="2:5">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
         <v>605</v>
       </c>
@@ -7874,7 +7265,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="2:5">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
         <v>607</v>
       </c>
@@ -7888,7 +7279,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="308" spans="2:5">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
         <v>609</v>
       </c>
@@ -7902,7 +7293,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="309" spans="2:5">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
         <v>611</v>
       </c>
@@ -7916,7 +7307,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="310" spans="2:5">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
         <v>613</v>
       </c>
@@ -7930,7 +7321,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="311" spans="2:5">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
         <v>615</v>
       </c>
@@ -7938,7 +7329,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="312" spans="2:5">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
         <v>616</v>
       </c>
@@ -7952,7 +7343,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="313" spans="2:5">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
         <v>618</v>
       </c>
@@ -7966,7 +7357,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="314" spans="2:5">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
         <v>620</v>
       </c>
@@ -7980,7 +7371,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="315" spans="2:5">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
         <v>622</v>
       </c>
@@ -7994,7 +7385,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="316" spans="2:5">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
         <v>624</v>
       </c>
@@ -8008,7 +7399,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="317" spans="2:5">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
         <v>626</v>
       </c>
@@ -8022,7 +7413,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="318" spans="2:5">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
         <v>628</v>
       </c>
@@ -8036,7 +7427,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="319" spans="2:5">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
         <v>630</v>
       </c>
@@ -8050,7 +7441,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="320" spans="2:5">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
         <v>632</v>
       </c>
@@ -8064,7 +7455,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="321" spans="2:5">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
         <v>634</v>
       </c>
@@ -8078,7 +7469,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="322" spans="2:5">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
         <v>636</v>
       </c>
@@ -8086,7 +7477,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="323" spans="2:5">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" t="s">
         <v>637</v>
       </c>
@@ -8100,7 +7491,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="324" spans="2:5">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" t="s">
         <v>639</v>
       </c>
@@ -8114,7 +7505,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="325" spans="2:5">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>641</v>
       </c>
@@ -8128,7 +7519,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="326" spans="2:5">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" t="s">
         <v>643</v>
       </c>
@@ -8142,7 +7533,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="327" spans="2:5">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" t="s">
         <v>645</v>
       </c>
@@ -8156,7 +7547,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="328" spans="2:5">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
         <v>647</v>
       </c>
@@ -8170,7 +7561,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="329" spans="2:5">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
         <v>649</v>
       </c>
@@ -8184,7 +7575,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="330" spans="2:5">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" t="s">
         <v>651</v>
       </c>
@@ -8198,7 +7589,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="331" spans="2:5">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
         <v>653</v>
       </c>
@@ -8212,7 +7603,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="332" spans="2:5">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
         <v>655</v>
       </c>
@@ -8226,7 +7617,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="333" spans="2:5">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" t="s">
         <v>657</v>
       </c>
@@ -8240,7 +7631,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="334" spans="2:5">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
         <v>659</v>
       </c>
@@ -8254,7 +7645,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="335" spans="2:5">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" t="s">
         <v>661</v>
       </c>
@@ -8268,7 +7659,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="336" spans="2:5">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>663</v>
       </c>
@@ -8282,7 +7673,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="337" spans="2:5">
+    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
         <v>665</v>
       </c>
@@ -8296,7 +7687,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="338" spans="2:5">
+    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>667</v>
       </c>
@@ -8310,7 +7701,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="339" spans="2:5">
+    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>669</v>
       </c>
@@ -8324,7 +7715,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="340" spans="2:5">
+    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
         <v>671</v>
       </c>
@@ -8338,7 +7729,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="341" spans="2:5">
+    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
         <v>673</v>
       </c>
@@ -8352,7 +7743,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="342" spans="2:5">
+    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
         <v>675</v>
       </c>
@@ -8366,12 +7757,12 @@
         <v>548</v>
       </c>
     </row>
-    <row r="343" spans="2:2">
+    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B343" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="344" spans="2:6">
+    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B344" t="s">
         <v>678</v>
       </c>
@@ -8388,7 +7779,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="345" spans="2:6">
+    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B345" t="s">
         <v>682</v>
       </c>
@@ -8405,7 +7796,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="346" spans="2:6">
+    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
         <v>684</v>
       </c>
@@ -8422,7 +7813,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="347" spans="2:6">
+    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B347" t="s">
         <v>686</v>
       </c>
@@ -8439,7 +7830,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="348" spans="2:6">
+    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B348" t="s">
         <v>688</v>
       </c>
@@ -8456,7 +7847,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="349" spans="2:6">
+    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B349" t="s">
         <v>690</v>
       </c>
@@ -8473,7 +7864,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="350" spans="2:6">
+    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B350" t="s">
         <v>692</v>
       </c>
@@ -8490,7 +7881,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="351" spans="2:6">
+    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B351" t="s">
         <v>694</v>
       </c>
@@ -8507,7 +7898,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="352" spans="2:6">
+    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B352" t="s">
         <v>696</v>
       </c>
@@ -8524,7 +7915,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="353" spans="2:6">
+    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B353" t="s">
         <v>698</v>
       </c>
@@ -8541,7 +7932,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="354" spans="2:6">
+    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>700</v>
       </c>
@@ -8558,7 +7949,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="355" spans="2:6">
+    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B355" t="s">
         <v>702</v>
       </c>
@@ -8575,7 +7966,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="356" spans="2:6">
+    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>704</v>
       </c>
@@ -8592,11 +7983,39 @@
         <v>46094</v>
       </c>
     </row>
+    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>707</v>
+      </c>
+      <c r="C357" t="s">
+        <v>706</v>
+      </c>
+      <c r="D357" t="s">
+        <v>20</v>
+      </c>
+      <c r="E357" t="s">
+        <v>681</v>
+      </c>
+      <c r="F357" s="2">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>708</v>
+      </c>
+      <c r="C358" t="s">
+        <v>709</v>
+      </c>
+      <c r="D358" t="s">
+        <v>20</v>
+      </c>
+      <c r="F358" s="2">
+        <v>46096</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G356" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:G356" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5E6643-0B99-4535-952E-3E412E9ED7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A05A9-5003-4333-907E-CABEC19B8602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="710">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -8010,6 +8010,9 @@
       <c r="D358" t="s">
         <v>20</v>
       </c>
+      <c r="E358" t="s">
+        <v>681</v>
+      </c>
       <c r="F358" s="2">
         <v>46096</v>
       </c>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A05A9-5003-4333-907E-CABEC19B8602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885A2F39-77BB-46D2-84A8-5859BA3FDE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2165,7 +2165,7 @@
     <t>315-python-train-func-chanels-normalization-vol-ofi.md</t>
   </si>
   <si>
-    <t>Исправить функции расчета каналов и их нормализации в dataset.py VOL, OFI. До этого все to была двойная нормализация и неправилньые формы логарифмирования Объемов, котоыре каждый урвоень считали отдельно и суммировали.</t>
+    <t>Исправить функции расчета каналов и их нормализации в dataset.py VOL, OFI. До этого все to была двойная нормализация и неправилньые формы логарифмирования Объемов, котоыре каждый урвоень считали отдельно и суммировали. В Задача 315-4 так же перенесли нормализацию в начало, до этого она номрализоввывала уже обработаныне данные.</t>
   </si>
 </sst>
 </file>
@@ -2188,6 +2188,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -2195,6 +2196,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885A2F39-77BB-46D2-84A8-5859BA3FDE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60D04F-BA99-4711-B310-4747DD5BA4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1080" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="712">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2166,6 +2166,12 @@
   </si>
   <si>
     <t>Исправить функции расчета каналов и их нормализации в dataset.py VOL, OFI. До этого все to была двойная нормализация и неправилньые формы логарифмирования Объемов, котоыре каждый урвоень считали отдельно и суммировали. В Задача 315-4 так же перенесли нормализацию в начало, до этого она номрализоввывала уже обработаныне данные.</t>
+  </si>
+  <si>
+    <t>316-python-train-chanels-price-micro-pastreturn-horizonts.md</t>
+  </si>
+  <si>
+    <t>Заменили 6 каналов на 7, теперь есть MicroPriceDev. Улучшение информативности каналов модели LiT. Канал Price  переделать, добавить микроструктуры. Канал PastRet разделить на 3 горизонта. вычислять за 10 , 50 и 100 тиков</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H358"/>
+  <dimension ref="A1:H359"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -8019,6 +8025,23 @@
         <v>46096</v>
       </c>
     </row>
+    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>710</v>
+      </c>
+      <c r="C359" t="s">
+        <v>711</v>
+      </c>
+      <c r="D359" t="s">
+        <v>20</v>
+      </c>
+      <c r="E359" t="s">
+        <v>681</v>
+      </c>
+      <c r="F359" s="2">
+        <v>46096</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G356" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60D04F-BA99-4711-B310-4747DD5BA4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD1BD1F-BB74-43E4-8A28-276405308941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1080" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="714">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2172,6 +2172,12 @@
   </si>
   <si>
     <t>Заменили 6 каналов на 7, теперь есть MicroPriceDev. Улучшение информативности каналов модели LiT. Канал Price  переделать, добавить микроструктуры. Канал PastRet разделить на 3 горизонта. вычислять за 10 , 50 и 100 тиков</t>
+  </si>
+  <si>
+    <t>317-python-fix-microprice-pastret-feature-quality.md</t>
+  </si>
+  <si>
+    <t>Создание 9 каналов вместо 6. Исправление качества входных фичей MicropriceDev и PastRet. Исправить формулу MicropriceDev. Убрать skip нормализации для канала 0. Расширить past_ret_cache до 3 лагов. Расширить _calculate_6_channels_raw до 9 каналов. Обновить _process_sample для 9 каналов: price_ch, vol_ch, imb_ch, ofi_ch, vib_ch, ret10_ch, ret50_ch, ret100_ch, spread_ch. Threshold проверили - работает правильно .чем выше он, тем больше Flat на распределение, не на предсказание.</t>
   </si>
 </sst>
 </file>
@@ -2514,7 +2520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H359"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -8039,7 +8045,24 @@
         <v>681</v>
       </c>
       <c r="F359" s="2">
-        <v>46096</v>
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B360" t="s">
+        <v>712</v>
+      </c>
+      <c r="C360" t="s">
+        <v>713</v>
+      </c>
+      <c r="D360" t="s">
+        <v>20</v>
+      </c>
+      <c r="E360" t="s">
+        <v>681</v>
+      </c>
+      <c r="F360" s="2">
+        <v>46098</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD1BD1F-BB74-43E4-8A28-276405308941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28791C7F-4E67-4ED9-ACC7-B484619079B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="465" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="420" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="716">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2178,6 +2178,12 @@
   </si>
   <si>
     <t>Создание 9 каналов вместо 6. Исправление качества входных фичей MicropriceDev и PastRet. Исправить формулу MicropriceDev. Убрать skip нормализации для канала 0. Расширить past_ret_cache до 3 лагов. Расширить _calculate_6_channels_raw до 9 каналов. Обновить _process_sample для 9 каналов: price_ch, vol_ch, imb_ch, ofi_ch, vib_ch, ret10_ch, ret50_ch, ret100_ch, spread_ch. Threshold проверили - работает правильно .чем выше он, тем больше Flat на распределение, не на предсказание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавление временной динамики в микроструктурные индикаторы LOB. Расширение с 9 до 13 каналов: +DeltaImb, DeltaSpread, CumOFI, ImbAccel. Переписать OFI на настоящий Cont-Kukanov-Stoikov (по last_update_id обновлениям стакана вместо diff(imbalance)). Исправить MicropriceDev: делить на spread/2 вместо spread. Сохранить last_update_id в пайплайне данных. </t>
+  </si>
+  <si>
+    <t>318-python-train-indicators-lob-temporal-dynamics-indicators.md</t>
   </si>
 </sst>
 </file>
@@ -2520,7 +2526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H360"/>
+  <dimension ref="A1:H361"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -8062,7 +8068,24 @@
         <v>681</v>
       </c>
       <c r="F360" s="2">
-        <v>46098</v>
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B361" t="s">
+        <v>715</v>
+      </c>
+      <c r="C361" t="s">
+        <v>714</v>
+      </c>
+      <c r="D361" t="s">
+        <v>20</v>
+      </c>
+      <c r="E361" t="s">
+        <v>681</v>
+      </c>
+      <c r="F361" s="2">
+        <v>46099</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28791C7F-4E67-4ED9-ACC7-B484619079B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1704D0-EDAE-4955-AD52-3300CB34A706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="420" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="930" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="719">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2184,6 +2184,15 @@
   </si>
   <si>
     <t>318-python-train-indicators-lob-temporal-dynamics-indicators.md</t>
+  </si>
+  <si>
+    <t>В файле info_Сравнение нашего бота с стандартной LiT.md есть сравение нашей моделью с Стандартом LiT. Взять оттуда рекомендации по индикаторам и другому, что стоит переделать. Например CumOFI не правильно</t>
+  </si>
+  <si>
+    <t>319-python-train-rework-lob-patching-preserve-spatial.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Переработка LOB Patching — сохранение пространственной информации стакана. Заменили CumOFI(кумулятивный) на стандартный OFI. Каналов теперь 11 вместо 13. Очистка шумных каналов в dataset.py. Переписание LOBPatching в layers.py. Адаптация LiTModel в lit_model.py. Обновление Normalizer и экспортных скриптов. </t>
   </si>
 </sst>
 </file>
@@ -2526,7 +2535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H361"/>
+  <dimension ref="A1:H365"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -8088,6 +8097,28 @@
         <v>46099</v>
       </c>
     </row>
+    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>717</v>
+      </c>
+      <c r="C362" t="s">
+        <v>718</v>
+      </c>
+      <c r="D362" t="s">
+        <v>20</v>
+      </c>
+      <c r="E362" t="s">
+        <v>681</v>
+      </c>
+      <c r="F362" s="2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C365" t="s">
+        <v>716</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G356" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1704D0-EDAE-4955-AD52-3300CB34A706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383481F-EE6D-41FA-BC1B-B5B1DBA741A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="930" windowWidth="19065" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="720">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2186,13 +2186,16 @@
     <t>318-python-train-indicators-lob-temporal-dynamics-indicators.md</t>
   </si>
   <si>
-    <t>В файле info_Сравнение нашего бота с стандартной LiT.md есть сравение нашей моделью с Стандартом LiT. Взять оттуда рекомендации по индикаторам и другому, что стоит переделать. Например CumOFI не правильно</t>
-  </si>
-  <si>
     <t>319-python-train-rework-lob-patching-preserve-spatial.md</t>
   </si>
   <si>
     <t xml:space="preserve">Переработка LOB Patching — сохранение пространственной информации стакана. Заменили CumOFI(кумулятивный) на стандартный OFI. Каналов теперь 11 вместо 13. Очистка шумных каналов в dataset.py. Переписание LOBPatching в layers.py. Адаптация LiTModel в lit_model.py. Обновление Normalizer и экспортных скриптов. </t>
+  </si>
+  <si>
+    <t>320-python-train-fix-post319-validation-stall-and-dataset-split.md</t>
+  </si>
+  <si>
+    <t>Устранить silent-stall после 319 на границе train→validation. Добавить phase-логи, guards для sanity-check и тяжелых epoch-end артефактов, вынести DataLoader/Trainer knobs в CLI, исправить split full_dataset/val/test на eval-mode и добавить диагностику saturation каналов до/после clamp.</t>
   </si>
 </sst>
 </file>
@@ -2262,7 +2265,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2535,17 +2538,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H365"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H363"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="52.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2588,7 +2591,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2596,7 +2599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2616,7 +2619,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2636,7 +2639,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2676,7 +2679,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -2716,7 +2719,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -2736,7 +2739,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -2756,7 +2759,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -2784,7 +2787,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -2804,7 +2807,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>48</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>50</v>
       </c>
@@ -2855,7 +2858,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>52</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>54</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>56</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>58</v>
       </c>
@@ -2923,7 +2926,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>60</v>
       </c>
@@ -2940,7 +2943,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>62</v>
       </c>
@@ -2957,7 +2960,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>64</v>
       </c>
@@ -2974,12 +2977,12 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>67</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>69</v>
       </c>
@@ -3013,7 +3016,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>71</v>
       </c>
@@ -3030,7 +3033,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>73</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>75</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>77</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>79</v>
       </c>
@@ -3098,7 +3101,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>81</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>83</v>
       </c>
@@ -3132,7 +3135,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>85</v>
       </c>
@@ -3149,7 +3152,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>87</v>
       </c>
@@ -3166,7 +3169,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>89</v>
       </c>
@@ -3183,12 +3186,12 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>92</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>94</v>
       </c>
@@ -3222,7 +3225,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>96</v>
       </c>
@@ -3239,7 +3242,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>98</v>
       </c>
@@ -3256,7 +3259,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>100</v>
       </c>
@@ -3273,7 +3276,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>102</v>
       </c>
@@ -3290,12 +3293,12 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>105</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>107</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>109</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>111</v>
       </c>
@@ -3363,7 +3366,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>113</v>
       </c>
@@ -3380,7 +3383,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>115</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>117</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>119</v>
       </c>
@@ -3431,7 +3434,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>121</v>
       </c>
@@ -3448,7 +3451,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>123</v>
       </c>
@@ -3465,7 +3468,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>125</v>
       </c>
@@ -3482,7 +3485,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>127</v>
       </c>
@@ -3499,12 +3502,12 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>130</v>
       </c>
@@ -3521,7 +3524,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>132</v>
       </c>
@@ -3538,7 +3541,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>134</v>
       </c>
@@ -3555,7 +3558,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>136</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>138</v>
       </c>
@@ -3589,7 +3592,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>140</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>142</v>
       </c>
@@ -3623,7 +3626,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>144</v>
       </c>
@@ -3640,7 +3643,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>146</v>
       </c>
@@ -3657,7 +3660,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>148</v>
       </c>
@@ -3674,12 +3677,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>151</v>
       </c>
@@ -3696,7 +3699,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>153</v>
       </c>
@@ -3713,7 +3716,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>155</v>
       </c>
@@ -3730,7 +3733,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>157</v>
       </c>
@@ -3747,7 +3750,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>159</v>
       </c>
@@ -3764,7 +3767,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>161</v>
       </c>
@@ -3781,7 +3784,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>164</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>166</v>
       </c>
@@ -3815,7 +3818,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>168</v>
       </c>
@@ -3832,7 +3835,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>170</v>
       </c>
@@ -3849,12 +3852,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>173</v>
       </c>
@@ -3871,7 +3874,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>175</v>
       </c>
@@ -3888,7 +3891,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>177</v>
       </c>
@@ -3905,7 +3908,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>179</v>
       </c>
@@ -3922,7 +3925,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>181</v>
       </c>
@@ -3939,12 +3942,12 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>184</v>
       </c>
@@ -3961,7 +3964,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>186</v>
       </c>
@@ -3978,7 +3981,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>188</v>
       </c>
@@ -3995,7 +3998,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>190</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>192</v>
       </c>
@@ -4029,12 +4032,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>195</v>
       </c>
@@ -4051,7 +4054,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>198</v>
       </c>
@@ -4068,7 +4071,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>200</v>
       </c>
@@ -4085,7 +4088,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>202</v>
       </c>
@@ -4102,7 +4105,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>204</v>
       </c>
@@ -4122,12 +4125,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>208</v>
       </c>
@@ -4144,7 +4147,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>210</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>212</v>
       </c>
@@ -4178,7 +4181,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>214</v>
       </c>
@@ -4195,7 +4198,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>216</v>
       </c>
@@ -4212,12 +4215,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>219</v>
       </c>
@@ -4234,7 +4237,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>221</v>
       </c>
@@ -4251,7 +4254,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>223</v>
       </c>
@@ -4268,7 +4271,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>225</v>
       </c>
@@ -4285,7 +4288,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>227</v>
       </c>
@@ -4302,12 +4305,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>230</v>
       </c>
@@ -4324,7 +4327,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>232</v>
       </c>
@@ -4341,7 +4344,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>234</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>236</v>
       </c>
@@ -4375,7 +4378,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>238</v>
       </c>
@@ -4392,12 +4395,12 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>241</v>
       </c>
@@ -4414,7 +4417,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>243</v>
       </c>
@@ -4431,7 +4434,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>245</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>247</v>
       </c>
@@ -4465,7 +4468,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>249</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>251</v>
       </c>
@@ -4499,7 +4502,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>253</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>255</v>
       </c>
@@ -4533,7 +4536,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>257</v>
       </c>
@@ -4550,7 +4553,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>259</v>
       </c>
@@ -4567,12 +4570,12 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>262</v>
       </c>
@@ -4589,7 +4592,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>264</v>
       </c>
@@ -4606,7 +4609,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>266</v>
       </c>
@@ -4623,7 +4626,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>268</v>
       </c>
@@ -4640,7 +4643,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>270</v>
       </c>
@@ -4657,7 +4660,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>272</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>274</v>
       </c>
@@ -4691,7 +4694,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>276</v>
       </c>
@@ -4708,7 +4711,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>278</v>
       </c>
@@ -4725,7 +4728,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>280</v>
       </c>
@@ -4742,12 +4745,12 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>283</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>285</v>
       </c>
@@ -4781,7 +4784,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>287</v>
       </c>
@@ -4798,7 +4801,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>289</v>
       </c>
@@ -4815,7 +4818,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>291</v>
       </c>
@@ -4832,7 +4835,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>293</v>
       </c>
@@ -4849,7 +4852,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>295</v>
       </c>
@@ -4866,7 +4869,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>297</v>
       </c>
@@ -4883,7 +4886,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>299</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>301</v>
       </c>
@@ -4917,12 +4920,12 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>304</v>
       </c>
@@ -4939,7 +4942,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>306</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>308</v>
       </c>
@@ -4973,7 +4976,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>310</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>312</v>
       </c>
@@ -5007,7 +5010,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>314</v>
       </c>
@@ -5024,7 +5027,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>316</v>
       </c>
@@ -5041,7 +5044,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>318</v>
       </c>
@@ -5061,7 +5064,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>321</v>
       </c>
@@ -5078,7 +5081,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>323</v>
       </c>
@@ -5095,12 +5098,12 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>326</v>
       </c>
@@ -5117,7 +5120,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>328</v>
       </c>
@@ -5134,7 +5137,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>330</v>
       </c>
@@ -5151,7 +5154,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>332</v>
       </c>
@@ -5168,7 +5171,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>334</v>
       </c>
@@ -5185,12 +5188,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>337</v>
       </c>
@@ -5207,7 +5210,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>339</v>
       </c>
@@ -5224,7 +5227,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>341</v>
       </c>
@@ -5241,7 +5244,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>343</v>
       </c>
@@ -5258,7 +5261,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>345</v>
       </c>
@@ -5275,12 +5278,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>348</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>350</v>
       </c>
@@ -5314,7 +5317,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>352</v>
       </c>
@@ -5331,7 +5334,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>354</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>356</v>
       </c>
@@ -5368,7 +5371,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>359</v>
       </c>
@@ -5385,7 +5388,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>361</v>
       </c>
@@ -5402,7 +5405,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>363</v>
       </c>
@@ -5419,7 +5422,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>365</v>
       </c>
@@ -5436,7 +5439,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>367</v>
       </c>
@@ -5453,12 +5456,12 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>370</v>
       </c>
@@ -5475,7 +5478,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>372</v>
       </c>
@@ -5492,7 +5495,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>374</v>
       </c>
@@ -5509,7 +5512,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>376</v>
       </c>
@@ -5526,7 +5529,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>378</v>
       </c>
@@ -5543,7 +5546,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>380</v>
       </c>
@@ -5560,7 +5563,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>382</v>
       </c>
@@ -5577,7 +5580,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>384</v>
       </c>
@@ -5594,7 +5597,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>386</v>
       </c>
@@ -5611,7 +5614,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>388</v>
       </c>
@@ -5631,12 +5634,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>392</v>
       </c>
@@ -5653,7 +5656,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>394</v>
       </c>
@@ -5670,7 +5673,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>396</v>
       </c>
@@ -5687,7 +5690,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>398</v>
       </c>
@@ -5704,7 +5707,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>400</v>
       </c>
@@ -5721,7 +5724,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>402</v>
       </c>
@@ -5738,7 +5741,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>404</v>
       </c>
@@ -5755,7 +5758,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>406</v>
       </c>
@@ -5772,7 +5775,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>408</v>
       </c>
@@ -5789,7 +5792,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>410</v>
       </c>
@@ -5806,12 +5809,12 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>413</v>
       </c>
@@ -5828,7 +5831,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>415</v>
       </c>
@@ -5845,7 +5848,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>417</v>
       </c>
@@ -5862,7 +5865,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>419</v>
       </c>
@@ -5879,7 +5882,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>421</v>
       </c>
@@ -5896,7 +5899,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>423</v>
       </c>
@@ -5913,7 +5916,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>425</v>
       </c>
@@ -5930,7 +5933,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>427</v>
       </c>
@@ -5947,7 +5950,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>429</v>
       </c>
@@ -5964,7 +5967,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>431</v>
       </c>
@@ -5981,12 +5984,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>434</v>
       </c>
@@ -6003,7 +6006,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>436</v>
       </c>
@@ -6020,7 +6023,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>438</v>
       </c>
@@ -6037,7 +6040,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>440</v>
       </c>
@@ -6054,7 +6057,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>442</v>
       </c>
@@ -6071,7 +6074,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>444</v>
       </c>
@@ -6088,7 +6091,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>446</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>448</v>
       </c>
@@ -6122,7 +6125,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>450</v>
       </c>
@@ -6139,7 +6142,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>452</v>
       </c>
@@ -6156,12 +6159,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>455</v>
       </c>
@@ -6178,7 +6181,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>457</v>
       </c>
@@ -6195,7 +6198,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>459</v>
       </c>
@@ -6212,7 +6215,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>461</v>
       </c>
@@ -6229,7 +6232,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>463</v>
       </c>
@@ -6246,12 +6249,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>466</v>
       </c>
@@ -6268,7 +6271,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>468</v>
       </c>
@@ -6285,7 +6288,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>470</v>
       </c>
@@ -6302,7 +6305,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>472</v>
       </c>
@@ -6319,7 +6322,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B238" s="4" t="s">
         <v>474</v>
       </c>
@@ -6339,12 +6342,12 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>478</v>
       </c>
@@ -6361,7 +6364,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>480</v>
       </c>
@@ -6378,7 +6381,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>482</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>484</v>
       </c>
@@ -6412,7 +6415,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>486</v>
       </c>
@@ -6429,12 +6432,12 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B245" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B246" t="s">
         <v>489</v>
       </c>
@@ -6451,7 +6454,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B247" t="s">
         <v>491</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B248" t="s">
         <v>493</v>
       </c>
@@ -6485,7 +6488,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B249" t="s">
         <v>495</v>
       </c>
@@ -6502,7 +6505,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="250" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B250" s="4" t="s">
         <v>497</v>
       </c>
@@ -6522,12 +6525,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B252" t="s">
         <v>502</v>
       </c>
@@ -6544,7 +6547,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B253" t="s">
         <v>504</v>
       </c>
@@ -6561,7 +6564,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>506</v>
       </c>
@@ -6578,7 +6581,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>508</v>
       </c>
@@ -6595,7 +6598,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>510</v>
       </c>
@@ -6612,12 +6615,12 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="257" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="258" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>513</v>
       </c>
@@ -6634,7 +6637,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="259" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B259" s="4" t="s">
         <v>515</v>
       </c>
@@ -6651,7 +6654,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="260" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B260" t="s">
         <v>519</v>
       </c>
@@ -6668,7 +6671,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="261" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B261" t="s">
         <v>521</v>
       </c>
@@ -6685,7 +6688,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="262" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B262" t="s">
         <v>523</v>
       </c>
@@ -6702,12 +6705,12 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="263" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B263" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>526</v>
       </c>
@@ -6724,7 +6727,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="265" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>528</v>
       </c>
@@ -6741,7 +6744,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="266" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>530</v>
       </c>
@@ -6758,7 +6761,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="267" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>532</v>
       </c>
@@ -6775,7 +6778,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="268" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>534</v>
       </c>
@@ -6792,12 +6795,12 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="269" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="270" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>537</v>
       </c>
@@ -6814,7 +6817,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="271" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>539</v>
       </c>
@@ -6831,7 +6834,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="272" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>541</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>543</v>
       </c>
@@ -6865,7 +6868,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>545</v>
       </c>
@@ -6882,7 +6885,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>547</v>
       </c>
@@ -6890,7 +6893,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>549</v>
       </c>
@@ -6904,7 +6907,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>551</v>
       </c>
@@ -6918,7 +6921,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>553</v>
       </c>
@@ -6932,7 +6935,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B279" t="s">
         <v>555</v>
       </c>
@@ -6946,7 +6949,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B280" t="s">
         <v>557</v>
       </c>
@@ -6960,7 +6963,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B281" t="s">
         <v>559</v>
       </c>
@@ -6968,7 +6971,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B282" t="s">
         <v>560</v>
       </c>
@@ -6982,7 +6985,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B283" t="s">
         <v>562</v>
       </c>
@@ -6996,7 +6999,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B284" t="s">
         <v>564</v>
       </c>
@@ -7010,7 +7013,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B285" t="s">
         <v>566</v>
       </c>
@@ -7024,7 +7027,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B286" t="s">
         <v>568</v>
       </c>
@@ -7038,7 +7041,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B287" t="s">
         <v>570</v>
       </c>
@@ -7046,7 +7049,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B288" t="s">
         <v>571</v>
       </c>
@@ -7060,7 +7063,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B289" t="s">
         <v>574</v>
       </c>
@@ -7074,7 +7077,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B290" t="s">
         <v>576</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B291" t="s">
         <v>578</v>
       </c>
@@ -7102,7 +7105,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B292" t="s">
         <v>580</v>
       </c>
@@ -7116,7 +7119,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B293" t="s">
         <v>582</v>
       </c>
@@ -7124,7 +7127,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B294" t="s">
         <v>583</v>
       </c>
@@ -7138,7 +7141,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B295" t="s">
         <v>585</v>
       </c>
@@ -7152,7 +7155,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B296" t="s">
         <v>587</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B297" t="s">
         <v>589</v>
       </c>
@@ -7180,7 +7183,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B298" t="s">
         <v>591</v>
       </c>
@@ -7194,7 +7197,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B299" t="s">
         <v>593</v>
       </c>
@@ -7202,7 +7205,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B300" t="s">
         <v>594</v>
       </c>
@@ -7216,7 +7219,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B301" t="s">
         <v>596</v>
       </c>
@@ -7230,7 +7233,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B302" t="s">
         <v>598</v>
       </c>
@@ -7244,7 +7247,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B303" t="s">
         <v>600</v>
       </c>
@@ -7258,7 +7261,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B304" t="s">
         <v>602</v>
       </c>
@@ -7272,7 +7275,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B305" t="s">
         <v>604</v>
       </c>
@@ -7280,7 +7283,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B306" t="s">
         <v>605</v>
       </c>
@@ -7294,7 +7297,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>607</v>
       </c>
@@ -7308,7 +7311,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>609</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>611</v>
       </c>
@@ -7336,7 +7339,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>613</v>
       </c>
@@ -7350,7 +7353,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>615</v>
       </c>
@@ -7358,7 +7361,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>616</v>
       </c>
@@ -7372,7 +7375,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>618</v>
       </c>
@@ -7386,7 +7389,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>620</v>
       </c>
@@ -7400,7 +7403,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>622</v>
       </c>
@@ -7414,7 +7417,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>624</v>
       </c>
@@ -7428,7 +7431,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>626</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>628</v>
       </c>
@@ -7456,7 +7459,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B319" t="s">
         <v>630</v>
       </c>
@@ -7470,7 +7473,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B320" t="s">
         <v>632</v>
       </c>
@@ -7484,7 +7487,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B321" t="s">
         <v>634</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B322" t="s">
         <v>636</v>
       </c>
@@ -7506,7 +7509,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B323" t="s">
         <v>637</v>
       </c>
@@ -7520,7 +7523,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B324" t="s">
         <v>639</v>
       </c>
@@ -7534,7 +7537,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B325" t="s">
         <v>641</v>
       </c>
@@ -7548,7 +7551,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B326" t="s">
         <v>643</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B327" t="s">
         <v>645</v>
       </c>
@@ -7576,7 +7579,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B328" t="s">
         <v>647</v>
       </c>
@@ -7590,7 +7593,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B329" t="s">
         <v>649</v>
       </c>
@@ -7604,7 +7607,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B330" t="s">
         <v>651</v>
       </c>
@@ -7618,7 +7621,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>653</v>
       </c>
@@ -7632,7 +7635,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>655</v>
       </c>
@@ -7646,7 +7649,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>657</v>
       </c>
@@ -7660,7 +7663,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>659</v>
       </c>
@@ -7674,7 +7677,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>661</v>
       </c>
@@ -7688,7 +7691,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>663</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>665</v>
       </c>
@@ -7716,7 +7719,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>667</v>
       </c>
@@ -7730,7 +7733,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B339" t="s">
         <v>669</v>
       </c>
@@ -7744,7 +7747,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B340" t="s">
         <v>671</v>
       </c>
@@ -7758,7 +7761,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B341" t="s">
         <v>673</v>
       </c>
@@ -7772,7 +7775,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B342" t="s">
         <v>675</v>
       </c>
@@ -7786,12 +7789,12 @@
         <v>548</v>
       </c>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B343" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B344" t="s">
         <v>678</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>682</v>
       </c>
@@ -7825,7 +7828,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>684</v>
       </c>
@@ -7842,7 +7845,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B347" t="s">
         <v>686</v>
       </c>
@@ -7859,7 +7862,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B348" t="s">
         <v>688</v>
       </c>
@@ -7876,7 +7879,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B349" t="s">
         <v>690</v>
       </c>
@@ -7893,7 +7896,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B350" t="s">
         <v>692</v>
       </c>
@@ -7910,7 +7913,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B351" t="s">
         <v>694</v>
       </c>
@@ -7927,7 +7930,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B352" t="s">
         <v>696</v>
       </c>
@@ -7944,7 +7947,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B353" t="s">
         <v>698</v>
       </c>
@@ -7961,7 +7964,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B354" t="s">
         <v>700</v>
       </c>
@@ -7978,7 +7981,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B355" t="s">
         <v>702</v>
       </c>
@@ -7995,7 +7998,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B356" t="s">
         <v>704</v>
       </c>
@@ -8012,7 +8015,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B357" t="s">
         <v>707</v>
       </c>
@@ -8029,7 +8032,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B358" t="s">
         <v>708</v>
       </c>
@@ -8046,7 +8049,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B359" t="s">
         <v>710</v>
       </c>
@@ -8063,7 +8066,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B360" t="s">
         <v>712</v>
       </c>
@@ -8080,7 +8083,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B361" t="s">
         <v>715</v>
       </c>
@@ -8097,12 +8100,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B362" t="s">
+        <v>716</v>
+      </c>
+      <c r="C362" t="s">
         <v>717</v>
-      </c>
-      <c r="C362" t="s">
-        <v>718</v>
       </c>
       <c r="D362" t="s">
         <v>20</v>
@@ -8114,9 +8117,18 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C365" t="s">
-        <v>716</v>
+    <row r="363" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B363" t="s">
+        <v>718</v>
+      </c>
+      <c r="C363" t="s">
+        <v>719</v>
+      </c>
+      <c r="D363" t="s">
+        <v>20</v>
+      </c>
+      <c r="F363" s="2">
+        <v>46104</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383481F-EE6D-41FA-BC1B-B5B1DBA741A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427EC54D-D2F0-4597-8E79-EA593D322645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="728">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2196,6 +2196,30 @@
   </si>
   <si>
     <t>Устранить silent-stall после 319 на границе train→validation. Добавить phase-логи, guards для sanity-check и тяжелых epoch-end артефактов, вынести DataLoader/Trainer knobs в CLI, исправить split full_dataset/val/test на eval-mode и добавить диагностику saturation каналов до/после clamp.</t>
+  </si>
+  <si>
+    <t>321-python-train-restore-compact-snapshot-patching-speed.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Убрать архитектурный регресс скорости после задачи 319. Вернуть компактный snapshot-style patching. Снизить вторичный runtime overhead. </t>
+  </si>
+  <si>
+    <t>322-python-train-refactoring-monolith-split-files.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рефакторинг train.py. Разделение его на несколько файлов,  он стал слишком большой. Перенесли в : train_cli.py , train_runtime.py, train_data.py, train_metadata.py, train_module.py, train_model_factory.py, train_optuna.py, train_cv.py, train_postprocess.py, </t>
+  </si>
+  <si>
+    <t>323-python-train-fix-ofi-delta-data-pipeline.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Исправление OFI/Delta pipeline в Python train. Перенести инициализацию update_id_raw , ofi_cache. Убрать diff(imbalance). Отделить масштабирование OFI/Delta. новый контракт OFI/Delta. </t>
+  </si>
+  <si>
+    <t>324-python-train-stabilization-dynamic-ofi-delta.md</t>
+  </si>
+  <si>
+    <t>Стабилизировать dynamic feature contract OFI, DeltaImb, DeltaSpread для LiT. Перевести DeltaImb и DeltaSpread на тот же event-consistent источник, что и OFI. Переделать fit dynamic-normalizer. Синхронизировать train-fit</t>
   </si>
 </sst>
 </file>
@@ -2205,11 +2229,35 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -2257,12 +2305,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2538,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H363"/>
+  <dimension ref="A1:H367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
@@ -8127,8 +8178,79 @@
       <c r="D363" t="s">
         <v>20</v>
       </c>
+      <c r="E363" t="s">
+        <v>681</v>
+      </c>
       <c r="F363" s="2">
         <v>46104</v>
+      </c>
+    </row>
+    <row r="364" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B364" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="D364" t="s">
+        <v>20</v>
+      </c>
+      <c r="E364" t="s">
+        <v>681</v>
+      </c>
+      <c r="F364" s="2">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="365" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B365" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D365" t="s">
+        <v>20</v>
+      </c>
+      <c r="E365" t="s">
+        <v>681</v>
+      </c>
+      <c r="F365" s="2">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="366" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B366" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="D366" t="s">
+        <v>20</v>
+      </c>
+      <c r="E366" t="s">
+        <v>681</v>
+      </c>
+      <c r="F366" s="2">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="367" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B367" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="D367" t="s">
+        <v>20</v>
+      </c>
+      <c r="E367" t="s">
+        <v>681</v>
+      </c>
+      <c r="F367" s="2">
+        <v>46106</v>
       </c>
     </row>
   </sheetData>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427EC54D-D2F0-4597-8E79-EA593D322645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34365CE4-65D0-4A24-9D59-001DFDA96C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="742">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2220,6 +2220,48 @@
   </si>
   <si>
     <t>Стабилизировать dynamic feature contract OFI, DeltaImb, DeltaSpread для LiT. Перевести DeltaImb и DeltaSpread на тот же event-consistent источник, что и OFI. Переделать fit dynamic-normalizer. Синхронизировать train-fit</t>
+  </si>
+  <si>
+    <t>325-python-train-fix-metrics-validation-contract.md</t>
+  </si>
+  <si>
+    <t>326-python-train-horizon-threshold-sweep-baseline.md</t>
+  </si>
+  <si>
+    <t>327-python-train-execution-aware-event-time-labeling.md</t>
+  </si>
+  <si>
+    <t>328-python-train-objective-calibration-decision-rule.md</t>
+  </si>
+  <si>
+    <t>329-python-train-purged-holdout-and-walkforward.md</t>
+  </si>
+  <si>
+    <t>330-python-train-channel-attribution-logging.md</t>
+  </si>
+  <si>
+    <t>331-python-train-freeze-dead-branches-and-simplify-pipeline.md</t>
+  </si>
+  <si>
+    <t>Исправить контракт валидационных метрик в train_module.py: убрать двойное логирование val_mcc из validation_step(), собрать все epoch-метрики только в on_validation_epoch_end(), починить compute_hft_metrics() и вынести edge_down в short-sign формате. Добавить coverage_directional, gross/net edge, precision/recall и единый primary key val_mcc_primary, который должен использоваться в train.py и train_cv.py для checkpoint/early stopping. Обновить train_cli.py новыми флагами metric contract и сохранить epoch-отчёт в JSON.</t>
+  </si>
+  <si>
+    <t>Добавить sweep-режим в train_cli.py и train.py, который запускает collect_sweep_baseline() из train_data.py без обучения модели. Для каждой пары (horizon, threshold) считать share_flat/up/down, trade_share, row_time_seconds, event_time_seconds, median_spread_bps, threshold_to_spread_ratio, subspread_target и отдельно фиксировать reference для плохого dynamic_threshold. Сохранять docs/sweep_baseline.csv/json, а затем запускать mini-train shortlist на top-k конфигурациях с фиксированной LiT без изменения архитектуры.</t>
+  </si>
+  <si>
+    <t>Переписать labels.py, расширив Labeler.__init__() параметрами label_mode, time_mode, event_time_column, cost_floor_bps, fee_bps, slippage_bps, use_spread_floor, и реализовать effective_threshold = max(static, spread_floor, cost_floor). Добавить future-index lookup по row/event/ms через helper вроде _map_future_indices(...), а в train_cli.py и train_data.py передавать новый label contract и пересчитывать class weights строго по новым label columns. Запретить сочетание label_mode=execution_mid_return со старым dynamic_threshold=True и добавить verification script scripts/event_time_label_check.py</t>
+  </si>
+  <si>
+    <t>В train_module.py и train_cli.py добавить objective-ablation флаги use_class_weights, multi_task, cls_loss_weight, vol_loss_weight и прогнать матрицу CE/Focal x weights on/off x cls_only/multi_task. Реализовать post-hoc calibration через helper fit_temperature_scaler() в utils.py и decision rule поверх calibrated probs с режимами argmax, confidence_gap, class_specific_thresholds, flat_bias. На валидации считать отдельно argmax_metrics и decision_rule_metrics, а результаты objective-ablation сохранять в CSV</t>
+  </si>
+  <si>
+    <t>В train_cli.py и train_data.py заменить старый split на purged_holdout и walk_forward, используя effective_purge_events = max(seq_len, max_horizon, max_lag, purge_buffer_events). В train.py и train_cv.py строить окна без leakage и логировать диапазоны train/val/test вместе с val_mcc_primary, coverage_directional, net_edge_total. Добавить режимный анализ по spread, volatility, activity в train_module.py и сохранять результаты holdout/walk-forward в отдельные артефакты.</t>
+  </si>
+  <si>
+    <t>Добавить attribution flags в train_cli.py и helper attribution в utils.py с методами grad_x_input и occlusion. В dataset.py зафиксировать единый CHANNEL_NAMES на 11 каналов, а в train_module.py считать attribution в on_validation_epoch_end() для general, predicted class, true class, correct, wrong. Сохранять artifacts/&lt;symbol&gt;/attribution/epoch_{epoch}.json/csv и печатать только top-5 каналов для Flat, Up, Down</t>
+  </si>
+  <si>
+    <t>В train_cli.py добавить baseline profile lit_scalping_baseline и флаг freeze_experimental_features, который отключает multi-horizon, distillation и прочие legacy-ветки без удаления кода. В train.py и train_module.py ввести startup invariant checks для label contract, metrics contract, split_strategy, decision_rule и совместимости stable profile. Зафиксировать единое дерево артефактов и состояние pipeline в docs/train_logs.md и docs/baselines.md.</t>
   </si>
 </sst>
 </file>
@@ -2229,11 +2271,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -2305,12 +2355,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2589,12 +2640,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H367"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="52.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" customWidth="1"/>
     <col min="4" max="4" width="8.44140625" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" customWidth="1"/>
   </cols>
@@ -8253,6 +8304,113 @@
         <v>46106</v>
       </c>
     </row>
+    <row r="368" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B368" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="C368" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="D368" t="s">
+        <v>20</v>
+      </c>
+      <c r="E368" t="s">
+        <v>681</v>
+      </c>
+      <c r="F368" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="369" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B369" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="C369" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="D369" t="s">
+        <v>20</v>
+      </c>
+      <c r="E369" t="s">
+        <v>681</v>
+      </c>
+      <c r="F369" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="370" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B370" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C370" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="D370" t="s">
+        <v>20</v>
+      </c>
+      <c r="E370" t="s">
+        <v>681</v>
+      </c>
+      <c r="F370" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="371" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B371" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="C371" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="D371" t="s">
+        <v>20</v>
+      </c>
+      <c r="F371" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="372" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B372" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="C372" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="D372" t="s">
+        <v>20</v>
+      </c>
+      <c r="F372" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="373" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B373" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="C373" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="D373" t="s">
+        <v>20</v>
+      </c>
+      <c r="F373" s="2">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="374" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B374" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="C374" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="D374" t="s">
+        <v>20</v>
+      </c>
+      <c r="F374" s="2">
+        <v>46108</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G356" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
+++ b/docs/АРХИТЕКТУРА-Neirobot-LiT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAX\PYTHON\NEURAL-BOTS\neirobot-lit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34365CE4-65D0-4A24-9D59-001DFDA96C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4616EA-DA2E-4DC9-A847-F56CBF841678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1908" yWindow="1416" windowWidth="14412" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АРХИТЕКТУРА" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="742">
   <si>
     <t>Примеры категорий</t>
   </si>
@@ -2261,7 +2261,7 @@
     <t>Добавить attribution flags в train_cli.py и helper attribution в utils.py с методами grad_x_input и occlusion. В dataset.py зафиксировать единый CHANNEL_NAMES на 11 каналов, а в train_module.py считать attribution в on_validation_epoch_end() для general, predicted class, true class, correct, wrong. Сохранять artifacts/&lt;symbol&gt;/attribution/epoch_{epoch}.json/csv и печатать только top-5 каналов для Flat, Up, Down</t>
   </si>
   <si>
-    <t>В train_cli.py добавить baseline profile lit_scalping_baseline и флаг freeze_experimental_features, который отключает multi-horizon, distillation и прочие legacy-ветки без удаления кода. В train.py и train_module.py ввести startup invariant checks для label contract, metrics contract, split_strategy, decision_rule и совместимости stable profile. Зафиксировать единое дерево артефактов и состояние pipeline в docs/train_logs.md и docs/baselines.md.</t>
+    <t>В train_cli.py добавить baseline profile lit_scalping_baseline и флаг freeze_experimental_features, который отключает multi-horizon, distillation и прочие legacy-ветки без удаления кода. В train.py и train_module.py ввести startup invariant checks для label contract, metrics contract, split_strategy, decision_rule и совместимости stable profile. Зафиксировать единое дерево артефактов и состояние pipeline в docs/train_logs.md и python_lab/src/baselines.md.</t>
   </si>
 </sst>
 </file>
@@ -2271,11 +2271,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -2355,12 +2363,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8365,6 +8374,9 @@
       <c r="D371" t="s">
         <v>20</v>
       </c>
+      <c r="E371" t="s">
+        <v>681</v>
+      </c>
       <c r="F371" s="2">
         <v>46108</v>
       </c>
@@ -8379,6 +8391,9 @@
       <c r="D372" t="s">
         <v>20</v>
       </c>
+      <c r="E372" t="s">
+        <v>681</v>
+      </c>
       <c r="F372" s="2">
         <v>46108</v>
       </c>
@@ -8393,6 +8408,9 @@
       <c r="D373" t="s">
         <v>20</v>
       </c>
+      <c r="E373" t="s">
+        <v>681</v>
+      </c>
       <c r="F373" s="2">
         <v>46108</v>
       </c>
@@ -8401,11 +8419,14 @@
       <c r="B374" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="C374" s="8" t="s">
+      <c r="C374" s="9" t="s">
         <v>741</v>
       </c>
       <c r="D374" t="s">
         <v>20</v>
+      </c>
+      <c r="E374" t="s">
+        <v>681</v>
       </c>
       <c r="F374" s="2">
         <v>46108</v>
